--- a/Ammoniak/Ammoniak_Brownfield_H2_N2_Höchst/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_H2_N2_Höchst/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02D8985-C669-4486-8D4A-AEACA71ECCCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4029E6-0F17-4EC1-B859-1538EF79F80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1331,6 +1331,16 @@
     <xf numFmtId="2" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1376,17 +1386,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1397,49 +1416,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1798,10 +1798,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="81" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1818,8 +1818,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="65"/>
-      <c r="B3" s="76"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="82"/>
       <c r="C3" t="s">
         <v>102</v>
       </c>
@@ -1834,8 +1834,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="65"/>
-      <c r="B4" s="76"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="82"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -1850,8 +1850,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="65"/>
-      <c r="B5" s="76"/>
+      <c r="A5" s="71"/>
+      <c r="B5" s="82"/>
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -1866,8 +1866,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="65"/>
-      <c r="B6" s="76"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="82"/>
       <c r="C6" t="s">
         <v>15</v>
       </c>
@@ -1882,8 +1882,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="65"/>
-      <c r="B7" s="76"/>
+      <c r="A7" s="71"/>
+      <c r="B7" s="82"/>
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -1898,8 +1898,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="65"/>
-      <c r="B8" s="77" t="s">
+      <c r="A8" s="71"/>
+      <c r="B8" s="83" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1916,8 +1916,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="65"/>
-      <c r="B9" s="76"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="82"/>
       <c r="C9" t="s">
         <v>105</v>
       </c>
@@ -1932,8 +1932,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="65"/>
-      <c r="B10" s="76"/>
+      <c r="A10" s="71"/>
+      <c r="B10" s="82"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
@@ -1948,8 +1948,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="65"/>
-      <c r="B11" s="76"/>
+      <c r="A11" s="71"/>
+      <c r="B11" s="82"/>
       <c r="C11" t="s">
         <v>13</v>
       </c>
@@ -1964,8 +1964,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="65"/>
-      <c r="B12" s="76"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="82"/>
       <c r="C12" t="s">
         <v>110</v>
       </c>
@@ -1980,8 +1980,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="65"/>
-      <c r="B13" s="76"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="82"/>
       <c r="C13" t="s">
         <v>109</v>
       </c>
@@ -1996,8 +1996,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="65"/>
-      <c r="B14" s="76"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="82"/>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -2012,8 +2012,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="65"/>
-      <c r="B15" s="78"/>
+      <c r="A15" s="71"/>
+      <c r="B15" s="84"/>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
@@ -2028,8 +2028,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="65"/>
-      <c r="B16" s="69" t="s">
+      <c r="A16" s="71"/>
+      <c r="B16" s="75" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
@@ -2047,8 +2047,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="65"/>
-      <c r="B17" s="69"/>
+      <c r="A17" s="71"/>
+      <c r="B17" s="75"/>
       <c r="C17" t="s">
         <v>12</v>
       </c>
@@ -2063,8 +2063,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="65"/>
-      <c r="B18" s="69"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="75"/>
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -2079,8 +2079,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="65"/>
-      <c r="B19" s="69"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="75"/>
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -2095,8 +2095,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="65"/>
-      <c r="B20" s="69"/>
+      <c r="A20" s="71"/>
+      <c r="B20" s="75"/>
       <c r="C20" t="s">
         <v>17</v>
       </c>
@@ -2111,10 +2111,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="70" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="74" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2131,8 +2131,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="65"/>
-      <c r="B22" s="69"/>
+      <c r="A22" s="71"/>
+      <c r="B22" s="75"/>
       <c r="C22" t="s">
         <v>13</v>
       </c>
@@ -2147,8 +2147,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="65"/>
-      <c r="B23" s="69"/>
+      <c r="A23" s="71"/>
+      <c r="B23" s="75"/>
       <c r="C23" t="s">
         <v>15</v>
       </c>
@@ -2163,8 +2163,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="65"/>
-      <c r="B24" s="69"/>
+      <c r="A24" s="71"/>
+      <c r="B24" s="75"/>
       <c r="C24" t="s">
         <v>22</v>
       </c>
@@ -2179,8 +2179,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="65"/>
-      <c r="B25" s="69"/>
+      <c r="A25" s="71"/>
+      <c r="B25" s="75"/>
       <c r="C25" t="s">
         <v>47</v>
       </c>
@@ -2195,8 +2195,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="65"/>
-      <c r="B26" s="69"/>
+      <c r="A26" s="71"/>
+      <c r="B26" s="75"/>
       <c r="C26" t="s">
         <v>48</v>
       </c>
@@ -2211,8 +2211,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="65"/>
-      <c r="B27" s="69"/>
+      <c r="A27" s="71"/>
+      <c r="B27" s="75"/>
       <c r="C27" t="s">
         <v>17</v>
       </c>
@@ -2227,8 +2227,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="65"/>
-      <c r="B28" s="69"/>
+      <c r="A28" s="71"/>
+      <c r="B28" s="75"/>
       <c r="C28" t="s">
         <v>114</v>
       </c>
@@ -2243,8 +2243,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="65"/>
-      <c r="B29" s="70" t="s">
+      <c r="A29" s="71"/>
+      <c r="B29" s="76" t="s">
         <v>258</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -2261,8 +2261,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="65"/>
-      <c r="B30" s="73"/>
+      <c r="A30" s="71"/>
+      <c r="B30" s="79"/>
       <c r="C30" s="51" t="s">
         <v>23</v>
       </c>
@@ -2278,8 +2278,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="65"/>
-      <c r="B31" s="73"/>
+      <c r="A31" s="71"/>
+      <c r="B31" s="79"/>
       <c r="C31" s="51" t="s">
         <v>18</v>
       </c>
@@ -2294,8 +2294,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="65"/>
-      <c r="B32" s="73"/>
+      <c r="A32" s="71"/>
+      <c r="B32" s="79"/>
       <c r="C32" s="51" t="s">
         <v>19</v>
       </c>
@@ -2310,8 +2310,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="65"/>
-      <c r="B33" s="73"/>
+      <c r="A33" s="71"/>
+      <c r="B33" s="79"/>
       <c r="C33" s="51" t="s">
         <v>47</v>
       </c>
@@ -2326,8 +2326,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="65"/>
-      <c r="B34" s="73"/>
+      <c r="A34" s="71"/>
+      <c r="B34" s="79"/>
       <c r="C34" s="51" t="s">
         <v>48</v>
       </c>
@@ -2342,8 +2342,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="65"/>
-      <c r="B35" s="73"/>
+      <c r="A35" s="71"/>
+      <c r="B35" s="79"/>
       <c r="C35" s="51" t="s">
         <v>115</v>
       </c>
@@ -2358,8 +2358,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="65"/>
-      <c r="B36" s="73"/>
+      <c r="A36" s="71"/>
+      <c r="B36" s="79"/>
       <c r="C36" s="51" t="s">
         <v>114</v>
       </c>
@@ -2374,8 +2374,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="65"/>
-      <c r="B37" s="73"/>
+      <c r="A37" s="71"/>
+      <c r="B37" s="79"/>
       <c r="C37" s="51" t="s">
         <v>15</v>
       </c>
@@ -2390,8 +2390,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="66"/>
-      <c r="B38" s="74"/>
+      <c r="A38" s="72"/>
+      <c r="B38" s="80"/>
       <c r="C38" s="14" t="s">
         <v>17</v>
       </c>
@@ -2406,7 +2406,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="64" t="s">
+      <c r="A39" s="70" t="s">
         <v>86</v>
       </c>
       <c r="B39" s="57" t="s">
@@ -2426,44 +2426,44 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="67"/>
-      <c r="B40" s="97" t="s">
+      <c r="A40" s="73"/>
+      <c r="B40" s="64" t="s">
         <v>302</v>
       </c>
-      <c r="C40" s="98" t="s">
+      <c r="C40" s="65" t="s">
         <v>303</v>
       </c>
-      <c r="D40" s="98" t="s">
+      <c r="D40" s="65" t="s">
         <v>304</v>
       </c>
-      <c r="E40" s="99">
-        <v>4.9500000000000002E-2</v>
-      </c>
-      <c r="F40" s="98" t="s">
+      <c r="E40" s="66">
+        <v>0.2</v>
+      </c>
+      <c r="F40" s="65" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="67"/>
-      <c r="B41" s="100" t="s">
+      <c r="A41" s="73"/>
+      <c r="B41" s="67" t="s">
         <v>299</v>
       </c>
-      <c r="C41" s="101" t="s">
+      <c r="C41" s="68" t="s">
         <v>300</v>
       </c>
-      <c r="D41" s="101" t="s">
+      <c r="D41" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="E41" s="102">
+      <c r="E41" s="69">
         <v>5</v>
       </c>
-      <c r="F41" s="101" t="s">
+      <c r="F41" s="68" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="65"/>
-      <c r="B42" s="70" t="s">
+      <c r="A42" s="71"/>
+      <c r="B42" s="76" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2480,8 +2480,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="65"/>
-      <c r="B43" s="69"/>
+      <c r="A43" s="71"/>
+      <c r="B43" s="75"/>
       <c r="C43" t="s">
         <v>12</v>
       </c>
@@ -2496,8 +2496,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="65"/>
-      <c r="B44" s="69"/>
+      <c r="A44" s="71"/>
+      <c r="B44" s="75"/>
       <c r="C44" t="s">
         <v>19</v>
       </c>
@@ -2512,8 +2512,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="65"/>
-      <c r="B45" s="69"/>
+      <c r="A45" s="71"/>
+      <c r="B45" s="75"/>
       <c r="C45" t="s">
         <v>20</v>
       </c>
@@ -2528,8 +2528,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="65"/>
-      <c r="B46" s="69"/>
+      <c r="A46" s="71"/>
+      <c r="B46" s="75"/>
       <c r="C46" t="s">
         <v>15</v>
       </c>
@@ -2544,8 +2544,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="65"/>
-      <c r="B47" s="69"/>
+      <c r="A47" s="71"/>
+      <c r="B47" s="75"/>
       <c r="C47" t="s">
         <v>82</v>
       </c>
@@ -2560,8 +2560,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="65"/>
-      <c r="B48" s="71"/>
+      <c r="A48" s="71"/>
+      <c r="B48" s="77"/>
       <c r="C48" s="5" t="s">
         <v>17</v>
       </c>
@@ -2576,8 +2576,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="65"/>
-      <c r="B49" s="70" t="s">
+      <c r="A49" s="71"/>
+      <c r="B49" s="76" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -2594,8 +2594,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="65"/>
-      <c r="B50" s="69"/>
+      <c r="A50" s="71"/>
+      <c r="B50" s="75"/>
       <c r="C50" t="s">
         <v>12</v>
       </c>
@@ -2610,8 +2610,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="65"/>
-      <c r="B51" s="69"/>
+      <c r="A51" s="71"/>
+      <c r="B51" s="75"/>
       <c r="C51" t="s">
         <v>19</v>
       </c>
@@ -2626,8 +2626,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="65"/>
-      <c r="B52" s="69"/>
+      <c r="A52" s="71"/>
+      <c r="B52" s="75"/>
       <c r="C52" t="s">
         <v>20</v>
       </c>
@@ -2642,8 +2642,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="65"/>
-      <c r="B53" s="69"/>
+      <c r="A53" s="71"/>
+      <c r="B53" s="75"/>
       <c r="C53" t="s">
         <v>15</v>
       </c>
@@ -2658,8 +2658,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="65"/>
-      <c r="B54" s="69"/>
+      <c r="A54" s="71"/>
+      <c r="B54" s="75"/>
       <c r="C54" t="s">
         <v>82</v>
       </c>
@@ -2674,8 +2674,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="66"/>
-      <c r="B55" s="72"/>
+      <c r="A55" s="72"/>
+      <c r="B55" s="78"/>
       <c r="C55" s="14" t="s">
         <v>17</v>
       </c>
@@ -2690,7 +2690,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="64" t="s">
+      <c r="A56" s="70" t="s">
         <v>90</v>
       </c>
       <c r="B56" s="16" t="s">
@@ -2710,7 +2710,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="65"/>
+      <c r="A57" s="71"/>
       <c r="B57" s="17" t="s">
         <v>93</v>
       </c>
@@ -2728,7 +2728,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="66"/>
+      <c r="A58" s="72"/>
       <c r="B58" s="1" t="s">
         <v>94</v>
       </c>
@@ -2800,10 +2800,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="92" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="96" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="28" t="s">
@@ -2818,8 +2818,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="85"/>
-      <c r="B3" s="80"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="98"/>
       <c r="C3" s="12" t="s">
         <v>136</v>
       </c>
@@ -2832,8 +2832,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="85"/>
-      <c r="B4" s="80"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="98"/>
       <c r="C4" s="12" t="s">
         <v>102</v>
       </c>
@@ -2846,8 +2846,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="85"/>
-      <c r="B5" s="80"/>
+      <c r="A5" s="94"/>
+      <c r="B5" s="98"/>
       <c r="C5" s="12" t="s">
         <v>172</v>
       </c>
@@ -2860,8 +2860,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="85"/>
-      <c r="B6" s="80"/>
+      <c r="A6" s="94"/>
+      <c r="B6" s="98"/>
       <c r="C6" s="12" t="s">
         <v>184</v>
       </c>
@@ -2874,8 +2874,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="85"/>
-      <c r="B7" s="80"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="98"/>
       <c r="C7" s="12" t="s">
         <v>202</v>
       </c>
@@ -2888,8 +2888,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="85"/>
-      <c r="B8" s="80"/>
+      <c r="A8" s="94"/>
+      <c r="B8" s="98"/>
       <c r="C8" s="12" t="s">
         <v>251</v>
       </c>
@@ -2902,8 +2902,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="85"/>
-      <c r="B9" s="80"/>
+      <c r="A9" s="94"/>
+      <c r="B9" s="98"/>
       <c r="C9" s="12" t="s">
         <v>216</v>
       </c>
@@ -2916,8 +2916,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="85"/>
-      <c r="B10" s="80"/>
+      <c r="A10" s="94"/>
+      <c r="B10" s="98"/>
       <c r="C10" s="12" t="s">
         <v>241</v>
       </c>
@@ -2930,13 +2930,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="85"/>
-      <c r="B11" s="80"/>
+      <c r="A11" s="94"/>
+      <c r="B11" s="98"/>
       <c r="E11" s="35"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="85"/>
-      <c r="B12" s="79" t="s">
+      <c r="A12" s="94"/>
+      <c r="B12" s="100" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="37" t="s">
@@ -2951,8 +2951,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="85"/>
-      <c r="B13" s="80"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="98"/>
       <c r="C13" s="12" t="s">
         <v>177</v>
       </c>
@@ -2965,8 +2965,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="85"/>
-      <c r="B14" s="80"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="98"/>
       <c r="C14" s="12" t="s">
         <v>180</v>
       </c>
@@ -2979,8 +2979,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="85"/>
-      <c r="B15" s="80"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="98"/>
       <c r="C15" s="12" t="s">
         <v>181</v>
       </c>
@@ -2993,8 +2993,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="85"/>
-      <c r="B16" s="80"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="98"/>
       <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
@@ -3007,8 +3007,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="85"/>
-      <c r="B17" s="80"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="98"/>
       <c r="C17" s="12" t="s">
         <v>184</v>
       </c>
@@ -3021,8 +3021,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="85"/>
-      <c r="B18" s="80"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="98"/>
       <c r="C18" s="12" t="s">
         <v>202</v>
       </c>
@@ -3035,8 +3035,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="85"/>
-      <c r="B19" s="80"/>
+      <c r="A19" s="94"/>
+      <c r="B19" s="98"/>
       <c r="C19" s="12" t="s">
         <v>251</v>
       </c>
@@ -3049,8 +3049,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="85"/>
-      <c r="B20" s="80"/>
+      <c r="A20" s="94"/>
+      <c r="B20" s="98"/>
       <c r="C20" s="12" t="s">
         <v>216</v>
       </c>
@@ -3063,8 +3063,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="85"/>
-      <c r="B21" s="80"/>
+      <c r="A21" s="94"/>
+      <c r="B21" s="98"/>
       <c r="C21" s="12" t="s">
         <v>241</v>
       </c>
@@ -3077,16 +3077,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="85"/>
-      <c r="B22" s="82"/>
+      <c r="A22" s="94"/>
+      <c r="B22" s="99"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
       <c r="E22" s="40"/>
       <c r="F22" s="39"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="85"/>
-      <c r="B23" s="87" t="s">
+      <c r="A23" s="94"/>
+      <c r="B23" s="89" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="12" t="s">
@@ -3101,8 +3101,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="85"/>
-      <c r="B24" s="87"/>
+      <c r="A24" s="94"/>
+      <c r="B24" s="89"/>
       <c r="C24" s="12" t="s">
         <v>136</v>
       </c>
@@ -3115,8 +3115,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
-      <c r="B25" s="87"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="89"/>
       <c r="C25" s="12" t="s">
         <v>102</v>
       </c>
@@ -3129,8 +3129,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="85"/>
-      <c r="B26" s="87"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="89"/>
       <c r="C26" s="12" t="s">
         <v>174</v>
       </c>
@@ -3143,8 +3143,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="85"/>
-      <c r="B27" s="87"/>
+      <c r="A27" s="94"/>
+      <c r="B27" s="89"/>
       <c r="C27" s="12" t="s">
         <v>184</v>
       </c>
@@ -3157,8 +3157,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="85"/>
-      <c r="B28" s="87"/>
+      <c r="A28" s="94"/>
+      <c r="B28" s="89"/>
       <c r="C28" s="12" t="s">
         <v>202</v>
       </c>
@@ -3171,8 +3171,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="85"/>
-      <c r="B29" s="87"/>
+      <c r="A29" s="94"/>
+      <c r="B29" s="89"/>
       <c r="C29" s="12" t="s">
         <v>251</v>
       </c>
@@ -3185,8 +3185,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="85"/>
-      <c r="B30" s="87"/>
+      <c r="A30" s="94"/>
+      <c r="B30" s="89"/>
       <c r="C30" s="12" t="s">
         <v>216</v>
       </c>
@@ -3199,8 +3199,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="85"/>
-      <c r="B31" s="87"/>
+      <c r="A31" s="94"/>
+      <c r="B31" s="89"/>
       <c r="C31" s="12" t="s">
         <v>241</v>
       </c>
@@ -3213,15 +3213,15 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="85"/>
-      <c r="B32" s="87"/>
+      <c r="A32" s="94"/>
+      <c r="B32" s="89"/>
       <c r="E32" s="35"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="83" t="s">
+      <c r="A33" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="89" t="s">
+      <c r="B33" s="101" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="28" t="s">
@@ -3236,8 +3236,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="85"/>
-      <c r="B34" s="87"/>
+      <c r="A34" s="94"/>
+      <c r="B34" s="89"/>
       <c r="C34" s="12" t="s">
         <v>140</v>
       </c>
@@ -3250,8 +3250,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="85"/>
-      <c r="B35" s="87"/>
+      <c r="A35" s="94"/>
+      <c r="B35" s="89"/>
       <c r="C35" s="12" t="s">
         <v>169</v>
       </c>
@@ -3264,8 +3264,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="85"/>
-      <c r="B36" s="87"/>
+      <c r="A36" s="94"/>
+      <c r="B36" s="89"/>
       <c r="C36" s="12" t="s">
         <v>170</v>
       </c>
@@ -3278,8 +3278,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="85"/>
-      <c r="B37" s="87"/>
+      <c r="A37" s="94"/>
+      <c r="B37" s="89"/>
       <c r="C37" s="12" t="s">
         <v>184</v>
       </c>
@@ -3292,8 +3292,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="85"/>
-      <c r="B38" s="87"/>
+      <c r="A38" s="94"/>
+      <c r="B38" s="89"/>
       <c r="C38" s="12" t="s">
         <v>202</v>
       </c>
@@ -3306,8 +3306,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="85"/>
-      <c r="B39" s="87"/>
+      <c r="A39" s="94"/>
+      <c r="B39" s="89"/>
       <c r="C39" s="12" t="s">
         <v>251</v>
       </c>
@@ -3320,8 +3320,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="85"/>
-      <c r="B40" s="87"/>
+      <c r="A40" s="94"/>
+      <c r="B40" s="89"/>
       <c r="C40" s="12" t="s">
         <v>216</v>
       </c>
@@ -3334,8 +3334,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="85"/>
-      <c r="B41" s="87"/>
+      <c r="A41" s="94"/>
+      <c r="B41" s="89"/>
       <c r="C41" s="12" t="s">
         <v>241</v>
       </c>
@@ -3348,13 +3348,13 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="85"/>
-      <c r="B42" s="87"/>
+      <c r="A42" s="94"/>
+      <c r="B42" s="89"/>
       <c r="E42" s="35"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="85"/>
-      <c r="B43" s="90" t="s">
+      <c r="A43" s="94"/>
+      <c r="B43" s="88" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="37" t="s">
@@ -3369,8 +3369,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="85"/>
-      <c r="B44" s="87"/>
+      <c r="A44" s="94"/>
+      <c r="B44" s="89"/>
       <c r="C44" s="12" t="s">
         <v>142</v>
       </c>
@@ -3383,8 +3383,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="85"/>
-      <c r="B45" s="80"/>
+      <c r="A45" s="94"/>
+      <c r="B45" s="98"/>
       <c r="C45" s="12" t="s">
         <v>140</v>
       </c>
@@ -3397,8 +3397,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="85"/>
-      <c r="B46" s="80"/>
+      <c r="A46" s="94"/>
+      <c r="B46" s="98"/>
       <c r="C46" s="12" t="s">
         <v>136</v>
       </c>
@@ -3411,8 +3411,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="85"/>
-      <c r="B47" s="80"/>
+      <c r="A47" s="94"/>
+      <c r="B47" s="98"/>
       <c r="C47" s="12" t="s">
         <v>157</v>
       </c>
@@ -3425,8 +3425,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="85"/>
-      <c r="B48" s="80"/>
+      <c r="A48" s="94"/>
+      <c r="B48" s="98"/>
       <c r="C48" s="12" t="s">
         <v>158</v>
       </c>
@@ -3439,8 +3439,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="85"/>
-      <c r="B49" s="80"/>
+      <c r="A49" s="94"/>
+      <c r="B49" s="98"/>
       <c r="C49" s="12" t="s">
         <v>184</v>
       </c>
@@ -3453,8 +3453,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="85"/>
-      <c r="B50" s="80"/>
+      <c r="A50" s="94"/>
+      <c r="B50" s="98"/>
       <c r="C50" s="12" t="s">
         <v>202</v>
       </c>
@@ -3467,8 +3467,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="85"/>
-      <c r="B51" s="80"/>
+      <c r="A51" s="94"/>
+      <c r="B51" s="98"/>
       <c r="C51" s="12" t="s">
         <v>251</v>
       </c>
@@ -3481,8 +3481,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="85"/>
-      <c r="B52" s="80"/>
+      <c r="A52" s="94"/>
+      <c r="B52" s="98"/>
       <c r="C52" s="12" t="s">
         <v>216</v>
       </c>
@@ -3495,8 +3495,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="85"/>
-      <c r="B53" s="80"/>
+      <c r="A53" s="94"/>
+      <c r="B53" s="98"/>
       <c r="C53" s="12" t="s">
         <v>241</v>
       </c>
@@ -3509,18 +3509,18 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="88"/>
-      <c r="B54" s="91"/>
+      <c r="A54" s="95"/>
+      <c r="B54" s="102"/>
       <c r="C54" s="43"/>
       <c r="D54" s="43"/>
       <c r="E54" s="44"/>
       <c r="F54" s="43"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="83" t="s">
+      <c r="A55" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="86" t="s">
+      <c r="B55" s="96" t="s">
         <v>87</v>
       </c>
       <c r="C55" s="28" t="s">
@@ -3535,8 +3535,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="85"/>
-      <c r="B56" s="80"/>
+      <c r="A56" s="94"/>
+      <c r="B56" s="98"/>
       <c r="C56" s="12" t="s">
         <v>200</v>
       </c>
@@ -3549,13 +3549,13 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="85"/>
-      <c r="B57" s="82"/>
+      <c r="A57" s="94"/>
+      <c r="B57" s="99"/>
       <c r="E57" s="33"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="85"/>
-      <c r="B58" s="92" t="s">
+      <c r="A58" s="94"/>
+      <c r="B58" s="85" t="s">
         <v>305</v>
       </c>
       <c r="C58" s="60" t="s">
@@ -3570,8 +3570,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="85"/>
-      <c r="B59" s="93"/>
+      <c r="A59" s="94"/>
+      <c r="B59" s="86"/>
       <c r="C59" s="62" t="s">
         <v>200</v>
       </c>
@@ -3584,16 +3584,16 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="85"/>
-      <c r="B60" s="94"/>
+      <c r="A60" s="94"/>
+      <c r="B60" s="87"/>
       <c r="C60" s="62"/>
       <c r="D60" s="62"/>
       <c r="E60" s="63"/>
       <c r="F60" s="62"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="85"/>
-      <c r="B61" s="90" t="s">
+      <c r="A61" s="94"/>
+      <c r="B61" s="88" t="s">
         <v>6</v>
       </c>
       <c r="C61" s="37" t="s">
@@ -3608,8 +3608,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="85"/>
-      <c r="B62" s="87"/>
+      <c r="A62" s="94"/>
+      <c r="B62" s="89"/>
       <c r="C62" s="12" t="s">
         <v>136</v>
       </c>
@@ -3622,8 +3622,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="85"/>
-      <c r="B63" s="87"/>
+      <c r="A63" s="94"/>
+      <c r="B63" s="89"/>
       <c r="C63" s="12" t="s">
         <v>152</v>
       </c>
@@ -3636,8 +3636,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="85"/>
-      <c r="B64" s="87"/>
+      <c r="A64" s="94"/>
+      <c r="B64" s="89"/>
       <c r="C64" s="12" t="s">
         <v>184</v>
       </c>
@@ -3650,8 +3650,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="85"/>
-      <c r="B65" s="87"/>
+      <c r="A65" s="94"/>
+      <c r="B65" s="89"/>
       <c r="C65" s="12" t="s">
         <v>202</v>
       </c>
@@ -3664,8 +3664,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="85"/>
-      <c r="B66" s="87"/>
+      <c r="A66" s="94"/>
+      <c r="B66" s="89"/>
       <c r="C66" s="12" t="s">
         <v>210</v>
       </c>
@@ -3678,8 +3678,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="85"/>
-      <c r="B67" s="87"/>
+      <c r="A67" s="94"/>
+      <c r="B67" s="89"/>
       <c r="C67" s="12" t="s">
         <v>251</v>
       </c>
@@ -3692,8 +3692,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="85"/>
-      <c r="B68" s="87"/>
+      <c r="A68" s="94"/>
+      <c r="B68" s="89"/>
       <c r="C68" s="12" t="s">
         <v>216</v>
       </c>
@@ -3706,8 +3706,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="85"/>
-      <c r="B69" s="87"/>
+      <c r="A69" s="94"/>
+      <c r="B69" s="89"/>
       <c r="C69" s="12" t="s">
         <v>241</v>
       </c>
@@ -3720,12 +3720,12 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="85"/>
-      <c r="B70" s="95"/>
+      <c r="A70" s="94"/>
+      <c r="B70" s="90"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="85"/>
-      <c r="B71" s="90" t="s">
+      <c r="A71" s="94"/>
+      <c r="B71" s="88" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="37" t="s">
@@ -3740,8 +3740,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="85"/>
-      <c r="B72" s="87"/>
+      <c r="A72" s="94"/>
+      <c r="B72" s="89"/>
       <c r="C72" s="12" t="s">
         <v>137</v>
       </c>
@@ -3754,8 +3754,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="85"/>
-      <c r="B73" s="87"/>
+      <c r="A73" s="94"/>
+      <c r="B73" s="89"/>
       <c r="C73" s="12" t="s">
         <v>150</v>
       </c>
@@ -3768,8 +3768,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="85"/>
-      <c r="B74" s="87"/>
+      <c r="A74" s="94"/>
+      <c r="B74" s="89"/>
       <c r="C74" s="12" t="s">
         <v>184</v>
       </c>
@@ -3782,8 +3782,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="85"/>
-      <c r="B75" s="87"/>
+      <c r="A75" s="94"/>
+      <c r="B75" s="89"/>
       <c r="C75" s="12" t="s">
         <v>202</v>
       </c>
@@ -3796,8 +3796,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="85"/>
-      <c r="B76" s="87"/>
+      <c r="A76" s="94"/>
+      <c r="B76" s="89"/>
       <c r="C76" s="12" t="s">
         <v>210</v>
       </c>
@@ -3810,8 +3810,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="85"/>
-      <c r="B77" s="87"/>
+      <c r="A77" s="94"/>
+      <c r="B77" s="89"/>
       <c r="C77" s="12" t="s">
         <v>251</v>
       </c>
@@ -3824,8 +3824,8 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="85"/>
-      <c r="B78" s="87"/>
+      <c r="A78" s="94"/>
+      <c r="B78" s="89"/>
       <c r="C78" s="12" t="s">
         <v>216</v>
       </c>
@@ -3838,8 +3838,8 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="85"/>
-      <c r="B79" s="87"/>
+      <c r="A79" s="94"/>
+      <c r="B79" s="89"/>
       <c r="C79" s="12" t="s">
         <v>241</v>
       </c>
@@ -3852,14 +3852,14 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="88"/>
-      <c r="B80" s="96"/>
+      <c r="A80" s="95"/>
+      <c r="B80" s="91"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="83" t="s">
+      <c r="A81" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="86" t="s">
+      <c r="B81" s="96" t="s">
         <v>87</v>
       </c>
       <c r="C81" s="28" t="s">
@@ -3874,8 +3874,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="84"/>
-      <c r="B82" s="81"/>
+      <c r="A82" s="93"/>
+      <c r="B82" s="97"/>
       <c r="C82" s="55" t="s">
         <v>293</v>
       </c>
@@ -3888,8 +3888,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="85"/>
-      <c r="B83" s="80"/>
+      <c r="A83" s="94"/>
+      <c r="B83" s="98"/>
       <c r="C83" s="12" t="s">
         <v>196</v>
       </c>
@@ -3902,13 +3902,13 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="85"/>
-      <c r="B84" s="82"/>
+      <c r="A84" s="94"/>
+      <c r="B84" s="99"/>
       <c r="E84" s="35"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="85"/>
-      <c r="B85" s="79" t="s">
+      <c r="A85" s="94"/>
+      <c r="B85" s="100" t="s">
         <v>93</v>
       </c>
       <c r="C85" s="37" t="s">
@@ -3923,8 +3923,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="85"/>
-      <c r="B86" s="80"/>
+      <c r="A86" s="94"/>
+      <c r="B86" s="98"/>
       <c r="C86" s="12" t="s">
         <v>197</v>
       </c>
@@ -3937,16 +3937,16 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="85"/>
-      <c r="B87" s="82"/>
+      <c r="A87" s="94"/>
+      <c r="B87" s="99"/>
       <c r="C87" s="39"/>
       <c r="D87" s="39"/>
       <c r="E87" s="40"/>
       <c r="F87" s="39"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="85"/>
-      <c r="B88" s="79" t="s">
+      <c r="A88" s="94"/>
+      <c r="B88" s="100" t="s">
         <v>94</v>
       </c>
       <c r="C88" s="12" t="s">
@@ -3961,8 +3961,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="85"/>
-      <c r="B89" s="80"/>
+      <c r="A89" s="94"/>
+      <c r="B89" s="98"/>
       <c r="C89" s="12" t="s">
         <v>198</v>
       </c>
@@ -3975,18 +3975,18 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="88"/>
-      <c r="B90" s="91"/>
+      <c r="A90" s="95"/>
+      <c r="B90" s="102"/>
       <c r="C90" s="43"/>
       <c r="D90" s="43"/>
       <c r="E90" s="44"/>
       <c r="F90" s="43"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="83" t="s">
+      <c r="A91" s="92" t="s">
         <v>212</v>
       </c>
-      <c r="B91" s="86" t="s">
+      <c r="B91" s="96" t="s">
         <v>15</v>
       </c>
       <c r="C91" s="28" t="s">
@@ -4001,8 +4001,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="84"/>
-      <c r="B92" s="80"/>
+      <c r="A92" s="93"/>
+      <c r="B92" s="98"/>
       <c r="C92" s="12" t="s">
         <v>225</v>
       </c>
@@ -4014,16 +4014,16 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="84"/>
-      <c r="B93" s="82"/>
+      <c r="A93" s="93"/>
+      <c r="B93" s="99"/>
       <c r="C93" s="39"/>
       <c r="D93" s="39"/>
       <c r="E93" s="39"/>
       <c r="F93" s="39"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="84"/>
-      <c r="B94" s="79" t="s">
+      <c r="A94" s="93"/>
+      <c r="B94" s="100" t="s">
         <v>235</v>
       </c>
       <c r="C94" s="12" t="s">
@@ -4037,8 +4037,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="84"/>
-      <c r="B95" s="80"/>
+      <c r="A95" s="93"/>
+      <c r="B95" s="98"/>
       <c r="C95" s="12" t="s">
         <v>233</v>
       </c>
@@ -4050,8 +4050,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="84"/>
-      <c r="B96" s="80"/>
+      <c r="A96" s="93"/>
+      <c r="B96" s="98"/>
       <c r="C96" s="12" t="s">
         <v>229</v>
       </c>
@@ -4063,8 +4063,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="84"/>
-      <c r="B97" s="80"/>
+      <c r="A97" s="93"/>
+      <c r="B97" s="98"/>
       <c r="C97" s="12" t="s">
         <v>231</v>
       </c>
@@ -4076,8 +4076,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="84"/>
-      <c r="B98" s="80"/>
+      <c r="A98" s="93"/>
+      <c r="B98" s="98"/>
       <c r="C98" s="12" t="s">
         <v>234</v>
       </c>
@@ -4089,8 +4089,8 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="84"/>
-      <c r="B99" s="80"/>
+      <c r="A99" s="93"/>
+      <c r="B99" s="98"/>
       <c r="C99" s="12" t="s">
         <v>244</v>
       </c>
@@ -4102,8 +4102,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="84"/>
-      <c r="B100" s="79" t="s">
+      <c r="A100" s="93"/>
+      <c r="B100" s="100" t="s">
         <v>265</v>
       </c>
       <c r="C100" s="37" t="s">
@@ -4118,8 +4118,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="84"/>
-      <c r="B101" s="81"/>
+      <c r="A101" s="93"/>
+      <c r="B101" s="97"/>
       <c r="C101" s="55" t="s">
         <v>261</v>
       </c>
@@ -4132,8 +4132,8 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="84"/>
-      <c r="B102" s="81"/>
+      <c r="A102" s="93"/>
+      <c r="B102" s="97"/>
       <c r="C102" s="55" t="s">
         <v>276</v>
       </c>
@@ -4146,8 +4146,8 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="84"/>
-      <c r="B103" s="81"/>
+      <c r="A103" s="93"/>
+      <c r="B103" s="97"/>
       <c r="C103" s="55" t="s">
         <v>262</v>
       </c>
@@ -4160,8 +4160,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="84"/>
-      <c r="B104" s="81"/>
+      <c r="A104" s="93"/>
+      <c r="B104" s="97"/>
       <c r="C104" s="55" t="s">
         <v>278</v>
       </c>
@@ -4174,8 +4174,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="84"/>
-      <c r="B105" s="81"/>
+      <c r="A105" s="93"/>
+      <c r="B105" s="97"/>
       <c r="C105" s="55" t="s">
         <v>282</v>
       </c>
@@ -4188,8 +4188,8 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="84"/>
-      <c r="B106" s="81"/>
+      <c r="A106" s="93"/>
+      <c r="B106" s="97"/>
       <c r="C106" s="55" t="s">
         <v>259</v>
       </c>
@@ -4202,8 +4202,8 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="84"/>
-      <c r="B107" s="81"/>
+      <c r="A107" s="93"/>
+      <c r="B107" s="97"/>
       <c r="C107" s="55" t="s">
         <v>263</v>
       </c>
@@ -4216,8 +4216,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="84"/>
-      <c r="B108" s="81"/>
+      <c r="A108" s="93"/>
+      <c r="B108" s="97"/>
       <c r="C108" s="55" t="s">
         <v>264</v>
       </c>
@@ -4230,8 +4230,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="84"/>
-      <c r="B109" s="79" t="s">
+      <c r="A109" s="93"/>
+      <c r="B109" s="100" t="s">
         <v>283</v>
       </c>
       <c r="C109" s="37" t="s">
@@ -4246,8 +4246,8 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="84"/>
-      <c r="B110" s="81"/>
+      <c r="A110" s="93"/>
+      <c r="B110" s="97"/>
       <c r="C110" s="55" t="s">
         <v>286</v>
       </c>
@@ -4260,8 +4260,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="84"/>
-      <c r="B111" s="81"/>
+      <c r="A111" s="93"/>
+      <c r="B111" s="97"/>
       <c r="C111" s="55" t="s">
         <v>288</v>
       </c>
@@ -4274,8 +4274,8 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="84"/>
-      <c r="B112" s="81"/>
+      <c r="A112" s="93"/>
+      <c r="B112" s="97"/>
       <c r="C112" s="12" t="s">
         <v>289</v>
       </c>
@@ -4287,12 +4287,12 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="84"/>
-      <c r="B113" s="82"/>
+      <c r="A113" s="93"/>
+      <c r="B113" s="99"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="84"/>
-      <c r="B114" s="79" t="s">
+      <c r="A114" s="93"/>
+      <c r="B114" s="100" t="s">
         <v>294</v>
       </c>
       <c r="C114" s="37" t="s">
@@ -4307,8 +4307,8 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="84"/>
-      <c r="B115" s="80"/>
+      <c r="A115" s="93"/>
+      <c r="B115" s="98"/>
       <c r="C115" s="12" t="s">
         <v>297</v>
       </c>
@@ -4320,16 +4320,10 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="84"/>
+      <c r="A116" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="B71:B80"/>
-    <mergeCell ref="A81:A90"/>
-    <mergeCell ref="B81:B84"/>
-    <mergeCell ref="B85:B87"/>
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="B109:B113"/>
     <mergeCell ref="A91:A116"/>
@@ -4346,6 +4340,12 @@
     <mergeCell ref="B100:B108"/>
     <mergeCell ref="B91:B93"/>
     <mergeCell ref="A55:A80"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="B71:B80"/>
+    <mergeCell ref="A81:A90"/>
+    <mergeCell ref="B81:B84"/>
+    <mergeCell ref="B85:B87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Ammoniak/Ammoniak_Brownfield_H2_N2_Höchst/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_H2_N2_Höchst/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4029E6-0F17-4EC1-B859-1538EF79F80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1AA6E7-390B-46FB-84B0-1E9E93487AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -505,9 +505,6 @@
     <t>€/kWa</t>
   </si>
   <si>
-    <t>€/kg_H2 * h</t>
-  </si>
-  <si>
     <t>(%_Kapa)/h</t>
   </si>
   <si>
@@ -865,9 +862,6 @@
     <t>kW_el</t>
   </si>
   <si>
-    <t>€ h / kg a</t>
-  </si>
-  <si>
     <t>calc_cost_gesamt</t>
   </si>
   <si>
@@ -1073,6 +1067,12 @@
   </si>
   <si>
     <t>calc_n2bezug_kosten</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>€ / kg a</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1085,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1096,13 +1096,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1137,13 +1130,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFC000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1260,25 +1246,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1289,156 +1275,153 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1798,10 +1781,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="78" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1818,8 +1801,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="71"/>
-      <c r="B3" s="82"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="79"/>
       <c r="C3" t="s">
         <v>102</v>
       </c>
@@ -1830,12 +1813,12 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="71"/>
-      <c r="B4" s="82"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="79"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -1850,8 +1833,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="71"/>
-      <c r="B5" s="82"/>
+      <c r="A5" s="68"/>
+      <c r="B5" s="79"/>
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -1866,8 +1849,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="71"/>
-      <c r="B6" s="82"/>
+      <c r="A6" s="68"/>
+      <c r="B6" s="79"/>
       <c r="C6" t="s">
         <v>15</v>
       </c>
@@ -1882,8 +1865,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="71"/>
-      <c r="B7" s="82"/>
+      <c r="A7" s="68"/>
+      <c r="B7" s="79"/>
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -1898,8 +1881,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="71"/>
-      <c r="B8" s="83" t="s">
+      <c r="A8" s="68"/>
+      <c r="B8" s="80" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1916,8 +1899,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="71"/>
-      <c r="B9" s="82"/>
+      <c r="A9" s="68"/>
+      <c r="B9" s="79"/>
       <c r="C9" t="s">
         <v>105</v>
       </c>
@@ -1932,8 +1915,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
-      <c r="B10" s="82"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="79"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
@@ -1948,8 +1931,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="71"/>
-      <c r="B11" s="82"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="79"/>
       <c r="C11" t="s">
         <v>13</v>
       </c>
@@ -1964,8 +1947,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="71"/>
-      <c r="B12" s="82"/>
+      <c r="A12" s="68"/>
+      <c r="B12" s="79"/>
       <c r="C12" t="s">
         <v>110</v>
       </c>
@@ -1980,8 +1963,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="82"/>
+      <c r="A13" s="68"/>
+      <c r="B13" s="79"/>
       <c r="C13" t="s">
         <v>109</v>
       </c>
@@ -1996,8 +1979,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
-      <c r="B14" s="82"/>
+      <c r="A14" s="68"/>
+      <c r="B14" s="79"/>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -2012,8 +1995,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="71"/>
-      <c r="B15" s="84"/>
+      <c r="A15" s="68"/>
+      <c r="B15" s="81"/>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
@@ -2028,8 +2011,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="71"/>
-      <c r="B16" s="75" t="s">
+      <c r="A16" s="68"/>
+      <c r="B16" s="72" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
@@ -2047,8 +2030,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="71"/>
-      <c r="B17" s="75"/>
+      <c r="A17" s="68"/>
+      <c r="B17" s="72"/>
       <c r="C17" t="s">
         <v>12</v>
       </c>
@@ -2063,8 +2046,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="71"/>
-      <c r="B18" s="75"/>
+      <c r="A18" s="68"/>
+      <c r="B18" s="72"/>
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -2079,8 +2062,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="71"/>
-      <c r="B19" s="75"/>
+      <c r="A19" s="68"/>
+      <c r="B19" s="72"/>
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -2095,8 +2078,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="71"/>
-      <c r="B20" s="75"/>
+      <c r="A20" s="68"/>
+      <c r="B20" s="72"/>
       <c r="C20" t="s">
         <v>17</v>
       </c>
@@ -2111,10 +2094,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="71" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2126,13 +2109,13 @@
       <c r="E21" s="23">
         <v>490</v>
       </c>
-      <c r="F21" s="26" t="s">
-        <v>119</v>
+      <c r="F21" s="27" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="71"/>
-      <c r="B22" s="75"/>
+      <c r="A22" s="68"/>
+      <c r="B22" s="72"/>
       <c r="C22" t="s">
         <v>13</v>
       </c>
@@ -2147,8 +2130,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="71"/>
-      <c r="B23" s="75"/>
+      <c r="A23" s="68"/>
+      <c r="B23" s="72"/>
       <c r="C23" t="s">
         <v>15</v>
       </c>
@@ -2163,24 +2146,24 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="71"/>
-      <c r="B24" s="75"/>
+      <c r="A24" s="68"/>
+      <c r="B24" s="72"/>
       <c r="C24" t="s">
         <v>22</v>
       </c>
       <c r="D24" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="47">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="71"/>
-      <c r="B25" s="75"/>
+      <c r="A25" s="68"/>
+      <c r="B25" s="72"/>
       <c r="C25" t="s">
         <v>47</v>
       </c>
@@ -2195,8 +2178,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="71"/>
-      <c r="B26" s="75"/>
+      <c r="A26" s="68"/>
+      <c r="B26" s="72"/>
       <c r="C26" t="s">
         <v>48</v>
       </c>
@@ -2211,8 +2194,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="71"/>
-      <c r="B27" s="75"/>
+      <c r="A27" s="68"/>
+      <c r="B27" s="72"/>
       <c r="C27" t="s">
         <v>17</v>
       </c>
@@ -2227,8 +2210,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="71"/>
-      <c r="B28" s="75"/>
+      <c r="A28" s="68"/>
+      <c r="B28" s="72"/>
       <c r="C28" t="s">
         <v>114</v>
       </c>
@@ -2239,13 +2222,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="71"/>
-      <c r="B29" s="76" t="s">
-        <v>258</v>
+      <c r="A29" s="68"/>
+      <c r="B29" s="73" t="s">
+        <v>256</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>117</v>
@@ -2257,141 +2240,141 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="71"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="51" t="s">
+      <c r="A30" s="68"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="51" t="s">
+      <c r="D30" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="49">
         <f>E31*4</f>
         <v>424</v>
       </c>
-      <c r="F30" s="51" t="s">
+      <c r="F30" s="48" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="71"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="51" t="s">
+      <c r="A31" s="68"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="51" t="s">
+      <c r="D31" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="52">
+      <c r="E31" s="49">
         <v>106</v>
       </c>
-      <c r="F31" s="51" t="s">
+      <c r="F31" s="48" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="71"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="51" t="s">
+      <c r="A32" s="68"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="51" t="s">
+      <c r="D32" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="53">
+      <c r="E32" s="50">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F32" s="51" t="s">
+      <c r="F32" s="48" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="71"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="51" t="s">
+      <c r="A33" s="68"/>
+      <c r="B33" s="76"/>
+      <c r="C33" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="51" t="s">
+      <c r="D33" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="53">
+      <c r="E33" s="50">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F33" s="51" t="s">
+      <c r="F33" s="48" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="71"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="51" t="s">
+      <c r="A34" s="68"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="51" t="s">
+      <c r="D34" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="E34" s="53">
+      <c r="E34" s="50">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F34" s="51" t="s">
+      <c r="F34" s="48" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="71"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="51" t="s">
+      <c r="A35" s="68"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="52">
+      <c r="E35" s="49">
         <v>0.25</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F35" s="48" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="71"/>
-      <c r="B36" s="79"/>
-      <c r="C36" s="51" t="s">
+      <c r="A36" s="68"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="51" t="s">
+      <c r="D36" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="E36" s="53">
+      <c r="E36" s="50">
         <v>0</v>
       </c>
-      <c r="F36" s="51" t="s">
-        <v>121</v>
+      <c r="F36" s="48" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="71"/>
-      <c r="B37" s="79"/>
-      <c r="C37" s="51" t="s">
+      <c r="A37" s="68"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="51" t="s">
+      <c r="D37" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="54">
+      <c r="E37" s="51">
         <v>15</v>
       </c>
-      <c r="F37" s="51" t="s">
+      <c r="F37" s="48" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="72"/>
-      <c r="B38" s="80"/>
+      <c r="A38" s="69"/>
+      <c r="B38" s="77"/>
       <c r="C38" s="14" t="s">
         <v>17</v>
       </c>
@@ -2406,64 +2389,64 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="57" t="s">
+      <c r="B39" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="58" t="s">
+      <c r="D39" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="59">
+      <c r="E39" s="56">
         <v>0.1699</v>
       </c>
-      <c r="F39" s="58" t="s">
+      <c r="F39" s="55" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="73"/>
-      <c r="B40" s="64" t="s">
+      <c r="A40" s="70"/>
+      <c r="B40" s="61" t="s">
+        <v>300</v>
+      </c>
+      <c r="C40" s="62" t="s">
+        <v>301</v>
+      </c>
+      <c r="D40" s="62" t="s">
         <v>302</v>
       </c>
-      <c r="C40" s="65" t="s">
-        <v>303</v>
-      </c>
-      <c r="D40" s="65" t="s">
-        <v>304</v>
-      </c>
-      <c r="E40" s="66">
+      <c r="E40" s="63">
         <v>0.2</v>
       </c>
-      <c r="F40" s="65" t="s">
-        <v>271</v>
+      <c r="F40" s="62" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="73"/>
-      <c r="B41" s="67" t="s">
+      <c r="A41" s="70"/>
+      <c r="B41" s="64" t="s">
+        <v>297</v>
+      </c>
+      <c r="C41" s="65" t="s">
+        <v>298</v>
+      </c>
+      <c r="D41" s="65" t="s">
         <v>299</v>
       </c>
-      <c r="C41" s="68" t="s">
-        <v>300</v>
-      </c>
-      <c r="D41" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="E41" s="69">
+      <c r="E41" s="66">
         <v>5</v>
       </c>
-      <c r="F41" s="68" t="s">
-        <v>271</v>
+      <c r="F41" s="65" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="71"/>
-      <c r="B42" s="76" t="s">
+      <c r="A42" s="68"/>
+      <c r="B42" s="73" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2480,8 +2463,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="71"/>
-      <c r="B43" s="75"/>
+      <c r="A43" s="68"/>
+      <c r="B43" s="72"/>
       <c r="C43" t="s">
         <v>12</v>
       </c>
@@ -2496,8 +2479,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="71"/>
-      <c r="B44" s="75"/>
+      <c r="A44" s="68"/>
+      <c r="B44" s="72"/>
       <c r="C44" t="s">
         <v>19</v>
       </c>
@@ -2512,8 +2495,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="71"/>
-      <c r="B45" s="75"/>
+      <c r="A45" s="68"/>
+      <c r="B45" s="72"/>
       <c r="C45" t="s">
         <v>20</v>
       </c>
@@ -2528,8 +2511,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="71"/>
-      <c r="B46" s="75"/>
+      <c r="A46" s="68"/>
+      <c r="B46" s="72"/>
       <c r="C46" t="s">
         <v>15</v>
       </c>
@@ -2544,8 +2527,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="71"/>
-      <c r="B47" s="75"/>
+      <c r="A47" s="68"/>
+      <c r="B47" s="72"/>
       <c r="C47" t="s">
         <v>82</v>
       </c>
@@ -2560,8 +2543,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="71"/>
-      <c r="B48" s="77"/>
+      <c r="A48" s="68"/>
+      <c r="B48" s="74"/>
       <c r="C48" s="5" t="s">
         <v>17</v>
       </c>
@@ -2576,8 +2559,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="71"/>
-      <c r="B49" s="76" t="s">
+      <c r="A49" s="68"/>
+      <c r="B49" s="73" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -2594,8 +2577,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="71"/>
-      <c r="B50" s="75"/>
+      <c r="A50" s="68"/>
+      <c r="B50" s="72"/>
       <c r="C50" t="s">
         <v>12</v>
       </c>
@@ -2610,15 +2593,15 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="71"/>
-      <c r="B51" s="75"/>
+      <c r="A51" s="68"/>
+      <c r="B51" s="72"/>
       <c r="C51" t="s">
         <v>19</v>
       </c>
       <c r="D51" t="s">
         <v>64</v>
       </c>
-      <c r="E51" s="45">
+      <c r="E51" s="44">
         <v>12.68</v>
       </c>
       <c r="F51" s="25" t="s">
@@ -2626,15 +2609,15 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="71"/>
-      <c r="B52" s="75"/>
+      <c r="A52" s="68"/>
+      <c r="B52" s="72"/>
       <c r="C52" t="s">
         <v>20</v>
       </c>
       <c r="D52" t="s">
         <v>61</v>
       </c>
-      <c r="E52" s="49">
+      <c r="E52" s="46">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F52" t="s">
@@ -2642,8 +2625,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="71"/>
-      <c r="B53" s="75"/>
+      <c r="A53" s="68"/>
+      <c r="B53" s="72"/>
       <c r="C53" t="s">
         <v>15</v>
       </c>
@@ -2658,15 +2641,15 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="71"/>
-      <c r="B54" s="75"/>
+      <c r="A54" s="68"/>
+      <c r="B54" s="72"/>
       <c r="C54" t="s">
         <v>82</v>
       </c>
       <c r="D54" t="s">
         <v>79</v>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="26">
         <v>1000000</v>
       </c>
       <c r="F54" t="s">
@@ -2674,8 +2657,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="72"/>
-      <c r="B55" s="78"/>
+      <c r="A55" s="69"/>
+      <c r="B55" s="75"/>
       <c r="C55" s="14" t="s">
         <v>17</v>
       </c>
@@ -2690,7 +2673,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="70" t="s">
+      <c r="A56" s="67" t="s">
         <v>90</v>
       </c>
       <c r="B56" s="16" t="s">
@@ -2710,7 +2693,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="71"/>
+      <c r="A57" s="68"/>
       <c r="B57" s="17" t="s">
         <v>93</v>
       </c>
@@ -2728,7 +2711,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="72"/>
+      <c r="A58" s="69"/>
       <c r="B58" s="1" t="s">
         <v>94</v>
       </c>
@@ -2780,1550 +2763,1556 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="29" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="86" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="E2" s="31"/>
+      <c r="F2" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="28" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="94"/>
-      <c r="B3" s="98"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="83"/>
       <c r="C3" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E3" s="33"/>
+        <v>143</v>
+      </c>
+      <c r="E3" s="32"/>
       <c r="F3" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="94"/>
-      <c r="B4" s="98"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="12" t="s">
         <v>102</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" s="34"/>
+        <v>152</v>
+      </c>
+      <c r="E4" s="33"/>
       <c r="F4" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="94"/>
-      <c r="B5" s="98"/>
+      <c r="A5" s="88"/>
+      <c r="B5" s="83"/>
       <c r="C5" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E5" s="35"/>
+        <v>170</v>
+      </c>
+      <c r="E5" s="34"/>
       <c r="F5" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="94"/>
-      <c r="B6" s="98"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="83"/>
       <c r="C6" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" s="36"/>
+        <v>185</v>
+      </c>
+      <c r="E6" s="35"/>
       <c r="F6" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="94"/>
-      <c r="B7" s="98"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="83"/>
       <c r="C7" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="E7" s="36"/>
+        <v>204</v>
+      </c>
+      <c r="E7" s="35"/>
       <c r="F7" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="94"/>
-      <c r="B8" s="98"/>
+      <c r="A8" s="88"/>
+      <c r="B8" s="83"/>
       <c r="C8" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="E8" s="36"/>
+        <v>248</v>
+      </c>
+      <c r="E8" s="35"/>
       <c r="F8" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="94"/>
-      <c r="B9" s="98"/>
+      <c r="A9" s="88"/>
+      <c r="B9" s="83"/>
       <c r="C9" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="E9" s="36"/>
+        <v>214</v>
+      </c>
+      <c r="E9" s="35"/>
       <c r="F9" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="94"/>
-      <c r="B10" s="98"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="83"/>
       <c r="C10" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="36"/>
+        <v>247</v>
+      </c>
+      <c r="E10" s="35"/>
       <c r="F10" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="94"/>
-      <c r="B11" s="98"/>
-      <c r="E11" s="35"/>
+      <c r="A11" s="88"/>
+      <c r="B11" s="83"/>
+      <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="94"/>
-      <c r="B12" s="100" t="s">
+      <c r="A12" s="88"/>
+      <c r="B12" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="37" t="s">
+      <c r="C12" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="37"/>
+      <c r="F12" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="37" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="94"/>
-      <c r="B13" s="98"/>
+      <c r="A13" s="88"/>
+      <c r="B13" s="83"/>
       <c r="C13" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" s="32"/>
+      <c r="F13" s="12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="88"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="E13" s="33"/>
-      <c r="F13" s="12" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="94"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="12" t="s">
+      <c r="E14" s="32"/>
+      <c r="F14" s="32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="88"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="94"/>
-      <c r="B15" s="98"/>
-      <c r="C15" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="E15" s="35"/>
+      <c r="E15" s="34"/>
       <c r="F15" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="94"/>
-      <c r="B16" s="98"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="83"/>
       <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
       <c r="D16" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="88"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="94"/>
-      <c r="B17" s="98"/>
-      <c r="C17" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="12" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="94"/>
-      <c r="B18" s="98"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="83"/>
       <c r="C18" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E18" s="36"/>
+        <v>207</v>
+      </c>
+      <c r="E18" s="35"/>
       <c r="F18" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="94"/>
-      <c r="B19" s="98"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="83"/>
       <c r="C19" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="E19" s="36"/>
+        <v>254</v>
+      </c>
+      <c r="E19" s="35"/>
       <c r="F19" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="94"/>
-      <c r="B20" s="98"/>
+      <c r="A20" s="88"/>
+      <c r="B20" s="83"/>
       <c r="C20" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="E20" s="36"/>
+        <v>221</v>
+      </c>
+      <c r="E20" s="35"/>
       <c r="F20" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="94"/>
-      <c r="B21" s="98"/>
+      <c r="A21" s="88"/>
+      <c r="B21" s="83"/>
       <c r="C21" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E21" s="36"/>
+        <v>246</v>
+      </c>
+      <c r="E21" s="35"/>
       <c r="F21" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="94"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="39"/>
+      <c r="A22" s="88"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="94"/>
-      <c r="B23" s="89" t="s">
+      <c r="A23" s="88"/>
+      <c r="B23" s="90" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" s="33"/>
+        <v>130</v>
+      </c>
+      <c r="E23" s="32"/>
       <c r="F23" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="94"/>
-      <c r="B24" s="89"/>
+      <c r="A24" s="88"/>
+      <c r="B24" s="90"/>
       <c r="C24" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="33"/>
+        <v>144</v>
+      </c>
+      <c r="E24" s="32"/>
       <c r="F24" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="94"/>
-      <c r="B25" s="89"/>
+      <c r="A25" s="88"/>
+      <c r="B25" s="90"/>
       <c r="C25" s="12" t="s">
         <v>102</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E25" s="35"/>
+        <v>153</v>
+      </c>
+      <c r="E25" s="34"/>
       <c r="F25" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="94"/>
-      <c r="B26" s="89"/>
+      <c r="A26" s="88"/>
+      <c r="B26" s="90"/>
       <c r="C26" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" s="35"/>
+      <c r="F26" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D26" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="12" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="94"/>
-      <c r="B27" s="89"/>
+      <c r="A27" s="88"/>
+      <c r="B27" s="90"/>
       <c r="C27" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D27" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" s="35"/>
+      <c r="F27" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="88"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E28" s="35"/>
+      <c r="F28" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="88"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E29" s="35"/>
+      <c r="F29" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="88"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E30" s="34"/>
+      <c r="F30" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="88"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E31" s="34"/>
+      <c r="F31" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="88"/>
+      <c r="B32" s="90"/>
+      <c r="E32" s="34"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="92" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="40"/>
+      <c r="F33" s="27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="88"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="34"/>
+      <c r="F34" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="88"/>
+      <c r="B35" s="90"/>
+      <c r="C35" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="E35" s="35"/>
+      <c r="F35" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="88"/>
+      <c r="B36" s="90"/>
+      <c r="C36" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" s="34"/>
+      <c r="F36" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="88"/>
+      <c r="B37" s="90"/>
+      <c r="C37" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="94"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="D28" s="12" t="s">
+      <c r="E37" s="34"/>
+      <c r="F37" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="88"/>
+      <c r="B38" s="90"/>
+      <c r="C38" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="E28" s="36"/>
-      <c r="F28" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="94"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="E29" s="36"/>
-      <c r="F29" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="94"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="E38" s="34"/>
+      <c r="F38" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="88"/>
+      <c r="B39" s="90"/>
+      <c r="C39" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="E39" s="34"/>
+      <c r="F39" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="88"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="E30" s="35"/>
-      <c r="F30" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="94"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="E31" s="35"/>
-      <c r="F31" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="94"/>
-      <c r="B32" s="89"/>
-      <c r="E32" s="35"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="92" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="101" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="28" t="s">
+      <c r="E40" s="34"/>
+      <c r="F40" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="88"/>
+      <c r="B41" s="90"/>
+      <c r="C41" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E41" s="34"/>
+      <c r="F41" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="88"/>
+      <c r="B42" s="90"/>
+      <c r="E42" s="34"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="88"/>
+      <c r="B43" s="93" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43" s="41"/>
+      <c r="F43" s="36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="88"/>
+      <c r="B44" s="90"/>
+      <c r="C44" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44" s="34"/>
+      <c r="F44" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="88"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E45" s="32"/>
+      <c r="F45" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="47" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="94"/>
-      <c r="B34" s="89"/>
-      <c r="C34" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="35"/>
-      <c r="F34" s="48" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="94"/>
-      <c r="B35" s="89"/>
-      <c r="C35" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="E35" s="36"/>
-      <c r="F35" s="12" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="94"/>
-      <c r="B36" s="89"/>
-      <c r="C36" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E36" s="35"/>
-      <c r="F36" s="12" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="94"/>
-      <c r="B37" s="89"/>
-      <c r="C37" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="E37" s="35"/>
-      <c r="F37" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="94"/>
-      <c r="B38" s="89"/>
-      <c r="C38" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="94"/>
-      <c r="B39" s="89"/>
-      <c r="C39" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="E39" s="35"/>
-      <c r="F39" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="94"/>
-      <c r="B40" s="89"/>
-      <c r="C40" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="E40" s="35"/>
-      <c r="F40" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="94"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="E41" s="35"/>
-      <c r="F41" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="94"/>
-      <c r="B42" s="89"/>
-      <c r="E42" s="35"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="94"/>
-      <c r="B43" s="88" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" s="42"/>
-      <c r="F43" s="37" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="94"/>
-      <c r="B44" s="89"/>
-      <c r="C44" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E44" s="35"/>
-      <c r="F44" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="94"/>
-      <c r="B45" s="98"/>
-      <c r="C45" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="E45" s="33"/>
-      <c r="F45" s="12" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="94"/>
-      <c r="B46" s="98"/>
+      <c r="A46" s="88"/>
+      <c r="B46" s="83"/>
       <c r="C46" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="E46" s="33"/>
+        <v>236</v>
+      </c>
+      <c r="E46" s="32"/>
       <c r="F46" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="94"/>
-      <c r="B47" s="98"/>
+      <c r="A47" s="88"/>
+      <c r="B47" s="83"/>
       <c r="C47" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E47" s="32"/>
+      <c r="F47" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="88"/>
+      <c r="B48" s="83"/>
+      <c r="C48" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D48" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="E47" s="33"/>
-      <c r="F47" s="12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="94"/>
-      <c r="B48" s="98"/>
-      <c r="C48" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="E48" s="35"/>
+      <c r="E48" s="34"/>
       <c r="F48" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="94"/>
-      <c r="B49" s="98"/>
+      <c r="A49" s="88"/>
+      <c r="B49" s="83"/>
       <c r="C49" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E49" s="33"/>
+        <v>187</v>
+      </c>
+      <c r="E49" s="32"/>
       <c r="F49" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="94"/>
-      <c r="B50" s="98"/>
+      <c r="A50" s="88"/>
+      <c r="B50" s="83"/>
       <c r="C50" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="E50" s="35"/>
+        <v>203</v>
+      </c>
+      <c r="E50" s="34"/>
       <c r="F50" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="94"/>
-      <c r="B51" s="98"/>
+      <c r="A51" s="88"/>
+      <c r="B51" s="83"/>
       <c r="C51" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="E51" s="35"/>
+        <v>255</v>
+      </c>
+      <c r="E51" s="34"/>
       <c r="F51" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="94"/>
-      <c r="B52" s="98"/>
+      <c r="A52" s="88"/>
+      <c r="B52" s="83"/>
       <c r="C52" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="E52" s="35"/>
+        <v>218</v>
+      </c>
+      <c r="E52" s="34"/>
       <c r="F52" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="94"/>
-      <c r="B53" s="98"/>
+      <c r="A53" s="88"/>
+      <c r="B53" s="83"/>
       <c r="C53" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="E53" s="35"/>
+        <v>243</v>
+      </c>
+      <c r="E53" s="34"/>
       <c r="F53" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="95"/>
-      <c r="B54" s="102"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="43"/>
+      <c r="A54" s="91"/>
+      <c r="B54" s="94"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="42"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="92" t="s">
+      <c r="A55" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="96" t="s">
+      <c r="B55" s="89" t="s">
         <v>87</v>
       </c>
-      <c r="C55" s="28" t="s">
+      <c r="C55" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E55" s="40"/>
+      <c r="F55" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="D55" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="E55" s="41"/>
-      <c r="F55" s="28" t="s">
-        <v>148</v>
-      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="94"/>
-      <c r="B56" s="98"/>
+      <c r="A56" s="88"/>
+      <c r="B56" s="83"/>
       <c r="C56" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D56" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="E56" s="32"/>
+      <c r="F56" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="88"/>
+      <c r="B57" s="85"/>
+      <c r="E57" s="32"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="88"/>
+      <c r="B58" s="95" t="s">
+        <v>303</v>
+      </c>
+      <c r="C58" s="57" t="s">
+        <v>304</v>
+      </c>
+      <c r="D58" s="57" t="s">
+        <v>305</v>
+      </c>
+      <c r="E58" s="58"/>
+      <c r="F58" s="57" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="88"/>
+      <c r="B59" s="96"/>
+      <c r="C59" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="E56" s="33"/>
-      <c r="F56" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="94"/>
-      <c r="B57" s="99"/>
-      <c r="E57" s="33"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="94"/>
-      <c r="B58" s="85" t="s">
-        <v>305</v>
-      </c>
-      <c r="C58" s="60" t="s">
+      <c r="D59" s="59" t="s">
         <v>306</v>
       </c>
-      <c r="D58" s="60" t="s">
-        <v>307</v>
-      </c>
-      <c r="E58" s="61"/>
-      <c r="F58" s="60" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="94"/>
-      <c r="B59" s="86"/>
-      <c r="C59" s="62" t="s">
-        <v>200</v>
-      </c>
-      <c r="D59" s="62" t="s">
-        <v>308</v>
-      </c>
-      <c r="E59" s="63"/>
-      <c r="F59" s="62" t="s">
-        <v>195</v>
+      <c r="E59" s="60"/>
+      <c r="F59" s="59" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="94"/>
-      <c r="B60" s="87"/>
-      <c r="C60" s="62"/>
-      <c r="D60" s="62"/>
-      <c r="E60" s="63"/>
-      <c r="F60" s="62"/>
+      <c r="A60" s="88"/>
+      <c r="B60" s="97"/>
+      <c r="C60" s="59"/>
+      <c r="D60" s="59"/>
+      <c r="E60" s="60"/>
+      <c r="F60" s="59"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="94"/>
-      <c r="B61" s="88" t="s">
+      <c r="A61" s="88"/>
+      <c r="B61" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D61" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="E61" s="42"/>
-      <c r="F61" s="37" t="s">
+      <c r="C61" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61" s="36" t="s">
         <v>125</v>
       </c>
+      <c r="E61" s="41"/>
+      <c r="F61" s="36" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="94"/>
-      <c r="B62" s="89"/>
+      <c r="A62" s="88"/>
+      <c r="B62" s="90"/>
       <c r="C62" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E62" s="45"/>
+        <v>137</v>
+      </c>
+      <c r="E62" s="44"/>
       <c r="F62" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="94"/>
-      <c r="B63" s="89"/>
+      <c r="A63" s="88"/>
+      <c r="B63" s="90"/>
       <c r="C63" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E63" s="45"/>
+        <v>150</v>
+      </c>
+      <c r="E63" s="44"/>
       <c r="F63" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="94"/>
-      <c r="B64" s="89"/>
+      <c r="A64" s="88"/>
+      <c r="B64" s="90"/>
       <c r="C64" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="E64" s="33"/>
+        <v>186</v>
+      </c>
+      <c r="E64" s="32"/>
       <c r="F64" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="94"/>
-      <c r="B65" s="89"/>
+      <c r="A65" s="88"/>
+      <c r="B65" s="90"/>
       <c r="C65" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D65" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="D65" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="E65" s="36"/>
+      <c r="E65" s="35"/>
       <c r="F65" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="94"/>
-      <c r="B66" s="89"/>
+      <c r="A66" s="88"/>
+      <c r="B66" s="90"/>
       <c r="C66" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="D66" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="E66" s="33"/>
+      <c r="E66" s="32"/>
       <c r="F66" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="94"/>
-      <c r="B67" s="89"/>
+      <c r="A67" s="88"/>
+      <c r="B67" s="90"/>
       <c r="C67" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="D67" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="E67" s="33"/>
+      <c r="E67" s="32"/>
       <c r="F67" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="94"/>
-      <c r="B68" s="89"/>
+      <c r="A68" s="88"/>
+      <c r="B68" s="90"/>
       <c r="C68" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="E68" s="35"/>
+        <v>217</v>
+      </c>
+      <c r="E68" s="34"/>
       <c r="F68" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="94"/>
-      <c r="B69" s="89"/>
+      <c r="A69" s="88"/>
+      <c r="B69" s="90"/>
       <c r="C69" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="D69" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="E69" s="35"/>
+      <c r="E69" s="34"/>
       <c r="F69" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="94"/>
-      <c r="B70" s="90"/>
+      <c r="A70" s="88"/>
+      <c r="B70" s="98"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="94"/>
-      <c r="B71" s="88" t="s">
+      <c r="A71" s="88"/>
+      <c r="B71" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="E71" s="42"/>
-      <c r="F71" s="37" t="s">
-        <v>125</v>
+      <c r="C71" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D71" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="E71" s="41"/>
+      <c r="F71" s="36" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="94"/>
-      <c r="B72" s="89"/>
+      <c r="A72" s="88"/>
+      <c r="B72" s="90"/>
       <c r="C72" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E72" s="45"/>
+        <v>134</v>
+      </c>
+      <c r="E72" s="44"/>
       <c r="F72" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="94"/>
-      <c r="B73" s="89"/>
+      <c r="A73" s="88"/>
+      <c r="B73" s="90"/>
       <c r="C73" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="E73" s="45"/>
+        <v>148</v>
+      </c>
+      <c r="E73" s="44"/>
       <c r="F73" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="94"/>
-      <c r="B74" s="89"/>
+      <c r="A74" s="88"/>
+      <c r="B74" s="90"/>
       <c r="C74" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D74" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D74" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="E74" s="45"/>
+      <c r="E74" s="44"/>
       <c r="F74" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="94"/>
-      <c r="B75" s="89"/>
+      <c r="A75" s="88"/>
+      <c r="B75" s="90"/>
       <c r="C75" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="E75" s="36"/>
+        <v>200</v>
+      </c>
+      <c r="E75" s="35"/>
       <c r="F75" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="88"/>
+      <c r="B76" s="90"/>
+      <c r="C76" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E76" s="45"/>
+      <c r="F76" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="88"/>
+      <c r="B77" s="90"/>
+      <c r="C77" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="E77" s="45"/>
+      <c r="F77" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="88"/>
+      <c r="B78" s="90"/>
+      <c r="C78" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E78" s="34"/>
+      <c r="F78" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="88"/>
+      <c r="B79" s="90"/>
+      <c r="C79" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E79" s="34"/>
+      <c r="F79" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="91"/>
+      <c r="B80" s="99"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="86" t="s">
+        <v>90</v>
+      </c>
+      <c r="B81" s="89" t="s">
+        <v>87</v>
+      </c>
+      <c r="C81" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D81" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E81" s="31"/>
+      <c r="F81" s="27" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="87"/>
+      <c r="B82" s="84"/>
+      <c r="C82" s="52" t="s">
+        <v>291</v>
+      </c>
+      <c r="D82" s="52" t="s">
+        <v>290</v>
+      </c>
+      <c r="E82" s="53"/>
+      <c r="F82" s="52" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="88"/>
+      <c r="B83" s="83"/>
+      <c r="C83" s="12" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="94"/>
-      <c r="B76" s="89"/>
-      <c r="C76" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="E76" s="46"/>
-      <c r="F76" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="94"/>
-      <c r="B77" s="89"/>
-      <c r="C77" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="E77" s="46"/>
-      <c r="F77" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="94"/>
-      <c r="B78" s="89"/>
-      <c r="C78" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="E78" s="35"/>
-      <c r="F78" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="94"/>
-      <c r="B79" s="89"/>
-      <c r="C79" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="D79" s="12" t="s">
+      <c r="D83" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E83" s="34"/>
+      <c r="F83" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="88"/>
+      <c r="B84" s="85"/>
+      <c r="E84" s="34"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="88"/>
+      <c r="B85" s="82" t="s">
+        <v>93</v>
+      </c>
+      <c r="C85" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="D85" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="E85" s="41"/>
+      <c r="F85" s="36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="88"/>
+      <c r="B86" s="83"/>
+      <c r="C86" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E86" s="34"/>
+      <c r="F86" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="88"/>
+      <c r="B87" s="85"/>
+      <c r="C87" s="38"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="38"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="88"/>
+      <c r="B88" s="82" t="s">
+        <v>94</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E88" s="34"/>
+      <c r="F88" s="12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="88"/>
+      <c r="B89" s="83"/>
+      <c r="C89" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E89" s="34"/>
+      <c r="F89" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="91"/>
+      <c r="B90" s="94"/>
+      <c r="C90" s="42"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="43"/>
+      <c r="F90" s="42"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="86" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" s="89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="D91" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="E91" s="27"/>
+      <c r="F91" s="27" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="87"/>
+      <c r="B92" s="83"/>
+      <c r="C92" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="87"/>
+      <c r="B93" s="85"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="38"/>
+      <c r="F93" s="38"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="87"/>
+      <c r="B94" s="82" t="s">
+        <v>234</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="87"/>
+      <c r="B95" s="83"/>
+      <c r="C95" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="87"/>
+      <c r="B96" s="83"/>
+      <c r="C96" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="87"/>
+      <c r="B97" s="83"/>
+      <c r="C97" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="F97" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="87"/>
+      <c r="B98" s="83"/>
+      <c r="C98" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="F98" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="87"/>
+      <c r="B99" s="83"/>
+      <c r="C99" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="E79" s="35"/>
-      <c r="F79" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
-      <c r="B80" s="91"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="92" t="s">
-        <v>90</v>
-      </c>
-      <c r="B81" s="96" t="s">
-        <v>87</v>
-      </c>
-      <c r="C81" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="D81" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E81" s="32"/>
-      <c r="F81" s="28" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="93"/>
-      <c r="B82" s="97"/>
-      <c r="C82" s="55" t="s">
+      <c r="D99" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="87"/>
+      <c r="B100" s="82" t="s">
+        <v>263</v>
+      </c>
+      <c r="C100" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="D100" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="E100" s="36"/>
+      <c r="F100" s="36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="87"/>
+      <c r="B101" s="84"/>
+      <c r="C101" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="D101" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="87"/>
+      <c r="B102" s="84"/>
+      <c r="C102" s="52" t="s">
+        <v>274</v>
+      </c>
+      <c r="D102" s="52" t="s">
+        <v>273</v>
+      </c>
+      <c r="E102" s="52"/>
+      <c r="F102" s="52" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="87"/>
+      <c r="B103" s="84"/>
+      <c r="C103" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="D103" s="52" t="s">
+        <v>266</v>
+      </c>
+      <c r="E103" s="52"/>
+      <c r="F103" s="52" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="87"/>
+      <c r="B104" s="84"/>
+      <c r="C104" s="52" t="s">
+        <v>276</v>
+      </c>
+      <c r="D104" s="52" t="s">
+        <v>275</v>
+      </c>
+      <c r="E104" s="52"/>
+      <c r="F104" s="52" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="87"/>
+      <c r="B105" s="84"/>
+      <c r="C105" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="D105" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="E105" s="52"/>
+      <c r="F105" s="52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="87"/>
+      <c r="B106" s="84"/>
+      <c r="C106" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E106" s="52"/>
+      <c r="F106" s="52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="87"/>
+      <c r="B107" s="84"/>
+      <c r="C107" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="D107" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="E107" s="52"/>
+      <c r="F107" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="87"/>
+      <c r="B108" s="84"/>
+      <c r="C108" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="D108" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="E108" s="52"/>
+      <c r="F108" s="52" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="87"/>
+      <c r="B109" s="82" t="s">
+        <v>281</v>
+      </c>
+      <c r="C109" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="D109" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="E109" s="36"/>
+      <c r="F109" s="36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="87"/>
+      <c r="B110" s="84"/>
+      <c r="C110" s="52" t="s">
+        <v>284</v>
+      </c>
+      <c r="D110" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="E110" s="52"/>
+      <c r="F110" s="52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="87"/>
+      <c r="B111" s="84"/>
+      <c r="C111" s="52" t="s">
+        <v>286</v>
+      </c>
+      <c r="D111" s="52" t="s">
+        <v>288</v>
+      </c>
+      <c r="E111" s="52"/>
+      <c r="F111" s="52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="87"/>
+      <c r="B112" s="84"/>
+      <c r="C112" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="F112" s="12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="87"/>
+      <c r="B113" s="85"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="87"/>
+      <c r="B114" s="82" t="s">
+        <v>292</v>
+      </c>
+      <c r="C114" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="D82" s="55" t="s">
-        <v>292</v>
-      </c>
-      <c r="E82" s="56"/>
-      <c r="F82" s="55" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="94"/>
-      <c r="B83" s="98"/>
-      <c r="C83" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E83" s="35"/>
-      <c r="F83" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="94"/>
-      <c r="B84" s="99"/>
-      <c r="E84" s="35"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="94"/>
-      <c r="B85" s="100" t="s">
-        <v>93</v>
-      </c>
-      <c r="C85" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="D85" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="E85" s="42"/>
-      <c r="F85" s="37" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="94"/>
-      <c r="B86" s="98"/>
-      <c r="C86" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="E86" s="35"/>
-      <c r="F86" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="94"/>
-      <c r="B87" s="99"/>
-      <c r="C87" s="39"/>
-      <c r="D87" s="39"/>
-      <c r="E87" s="40"/>
-      <c r="F87" s="39"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="94"/>
-      <c r="B88" s="100" t="s">
-        <v>94</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E88" s="35"/>
-      <c r="F88" s="12" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="94"/>
-      <c r="B89" s="98"/>
-      <c r="C89" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="E89" s="35"/>
-      <c r="F89" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="95"/>
-      <c r="B90" s="102"/>
-      <c r="C90" s="43"/>
-      <c r="D90" s="43"/>
-      <c r="E90" s="44"/>
-      <c r="F90" s="43"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="92" t="s">
-        <v>212</v>
-      </c>
-      <c r="B91" s="96" t="s">
-        <v>15</v>
-      </c>
-      <c r="C91" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="D91" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="E91" s="28"/>
-      <c r="F91" s="28" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="93"/>
-      <c r="B92" s="98"/>
-      <c r="C92" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="F92" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="93"/>
-      <c r="B93" s="99"/>
-      <c r="C93" s="39"/>
-      <c r="D93" s="39"/>
-      <c r="E93" s="39"/>
-      <c r="F93" s="39"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="93"/>
-      <c r="B94" s="100" t="s">
-        <v>235</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="F94" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="93"/>
-      <c r="B95" s="98"/>
-      <c r="C95" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F95" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="93"/>
-      <c r="B96" s="98"/>
-      <c r="C96" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="F96" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="93"/>
-      <c r="B97" s="98"/>
-      <c r="C97" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="F97" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="93"/>
-      <c r="B98" s="98"/>
-      <c r="C98" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="F98" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="93"/>
-      <c r="B99" s="98"/>
-      <c r="C99" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F99" s="12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="93"/>
-      <c r="B100" s="100" t="s">
-        <v>265</v>
-      </c>
-      <c r="C100" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="D100" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="E100" s="37"/>
-      <c r="F100" s="37" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="93"/>
-      <c r="B101" s="97"/>
-      <c r="C101" s="55" t="s">
-        <v>261</v>
-      </c>
-      <c r="D101" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="E101" s="55"/>
-      <c r="F101" s="55" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="93"/>
-      <c r="B102" s="97"/>
-      <c r="C102" s="55" t="s">
-        <v>276</v>
-      </c>
-      <c r="D102" s="55" t="s">
-        <v>275</v>
-      </c>
-      <c r="E102" s="55"/>
-      <c r="F102" s="55" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="93"/>
-      <c r="B103" s="97"/>
-      <c r="C103" s="55" t="s">
-        <v>262</v>
-      </c>
-      <c r="D103" s="55" t="s">
-        <v>268</v>
-      </c>
-      <c r="E103" s="55"/>
-      <c r="F103" s="55" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="93"/>
-      <c r="B104" s="97"/>
-      <c r="C104" s="55" t="s">
-        <v>278</v>
-      </c>
-      <c r="D104" s="55" t="s">
-        <v>277</v>
-      </c>
-      <c r="E104" s="55"/>
-      <c r="F104" s="55" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="93"/>
-      <c r="B105" s="97"/>
-      <c r="C105" s="55" t="s">
-        <v>282</v>
-      </c>
-      <c r="D105" s="55" t="s">
-        <v>270</v>
-      </c>
-      <c r="E105" s="55"/>
-      <c r="F105" s="55" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="93"/>
-      <c r="B106" s="97"/>
-      <c r="C106" s="55" t="s">
-        <v>259</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="E106" s="55"/>
-      <c r="F106" s="55" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="93"/>
-      <c r="B107" s="97"/>
-      <c r="C107" s="55" t="s">
-        <v>263</v>
-      </c>
-      <c r="D107" s="55" t="s">
-        <v>272</v>
-      </c>
-      <c r="E107" s="55"/>
-      <c r="F107" s="12" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="93"/>
-      <c r="B108" s="97"/>
-      <c r="C108" s="55" t="s">
-        <v>264</v>
-      </c>
-      <c r="D108" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="E108" s="55"/>
-      <c r="F108" s="55" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="93"/>
-      <c r="B109" s="100" t="s">
-        <v>283</v>
-      </c>
-      <c r="C109" s="37" t="s">
-        <v>285</v>
-      </c>
-      <c r="D109" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="E109" s="37"/>
-      <c r="F109" s="37" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="93"/>
-      <c r="B110" s="97"/>
-      <c r="C110" s="55" t="s">
-        <v>286</v>
-      </c>
-      <c r="D110" s="55" t="s">
-        <v>287</v>
-      </c>
-      <c r="E110" s="55"/>
-      <c r="F110" s="55" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="93"/>
-      <c r="B111" s="97"/>
-      <c r="C111" s="55" t="s">
-        <v>288</v>
-      </c>
-      <c r="D111" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="E111" s="55"/>
-      <c r="F111" s="55" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="93"/>
-      <c r="B112" s="97"/>
-      <c r="C112" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="F112" s="12" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="93"/>
-      <c r="B113" s="99"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="93"/>
-      <c r="B114" s="100" t="s">
+      <c r="D114" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="C114" s="37" t="s">
+      <c r="E114" s="36"/>
+      <c r="F114" s="36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="87"/>
+      <c r="B115" s="83"/>
+      <c r="C115" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D114" s="37" t="s">
+      <c r="D115" s="12" t="s">
         <v>296</v>
-      </c>
-      <c r="E114" s="37"/>
-      <c r="F114" s="37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="93"/>
-      <c r="B115" s="98"/>
-      <c r="C115" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>298</v>
       </c>
       <c r="F115" s="12" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="93"/>
+      <c r="A116" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="B71:B80"/>
+    <mergeCell ref="A81:A90"/>
+    <mergeCell ref="B81:B84"/>
+    <mergeCell ref="B85:B87"/>
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="B109:B113"/>
     <mergeCell ref="A91:A116"/>
@@ -4340,12 +4329,6 @@
     <mergeCell ref="B100:B108"/>
     <mergeCell ref="B91:B93"/>
     <mergeCell ref="A55:A80"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="B71:B80"/>
-    <mergeCell ref="A81:A90"/>
-    <mergeCell ref="B81:B84"/>
-    <mergeCell ref="B85:B87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Ammoniak/Ammoniak_Brownfield_H2_N2_Höchst/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_H2_N2_Höchst/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_N2_Höchst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1AA6E7-390B-46FB-84B0-1E9E93487AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7080267F-69CA-441D-B21C-C21686C6AEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-53868" yWindow="3444" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="307">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1016,12 +1016,6 @@
   </si>
   <si>
     <t>calc_cost_nh3</t>
-  </si>
-  <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
   </si>
   <si>
     <t>Verkaufspreiseanalyse</t>
@@ -1246,7 +1240,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1304,7 +1298,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1369,17 +1362,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1390,38 +1392,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1781,10 +1774,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="77" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1801,8 +1794,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="68"/>
-      <c r="B3" s="79"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="78"/>
       <c r="C3" t="s">
         <v>102</v>
       </c>
@@ -1817,8 +1810,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="68"/>
-      <c r="B4" s="79"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="78"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -1826,15 +1819,15 @@
         <v>28</v>
       </c>
       <c r="E4" s="20">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="68"/>
-      <c r="B5" s="79"/>
+      <c r="A5" s="67"/>
+      <c r="B5" s="78"/>
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -1849,8 +1842,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="68"/>
-      <c r="B6" s="79"/>
+      <c r="A6" s="67"/>
+      <c r="B6" s="78"/>
       <c r="C6" t="s">
         <v>15</v>
       </c>
@@ -1865,8 +1858,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="68"/>
-      <c r="B7" s="79"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="78"/>
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -1881,8 +1874,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="68"/>
-      <c r="B8" s="80" t="s">
+      <c r="A8" s="67"/>
+      <c r="B8" s="79" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1899,8 +1892,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="68"/>
-      <c r="B9" s="79"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="78"/>
       <c r="C9" t="s">
         <v>105</v>
       </c>
@@ -1915,8 +1908,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="68"/>
-      <c r="B10" s="79"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="78"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
@@ -1931,8 +1924,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="68"/>
-      <c r="B11" s="79"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="78"/>
       <c r="C11" t="s">
         <v>13</v>
       </c>
@@ -1947,8 +1940,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="68"/>
-      <c r="B12" s="79"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="78"/>
       <c r="C12" t="s">
         <v>110</v>
       </c>
@@ -1963,8 +1956,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="68"/>
-      <c r="B13" s="79"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="78"/>
       <c r="C13" t="s">
         <v>109</v>
       </c>
@@ -1979,8 +1972,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="68"/>
-      <c r="B14" s="79"/>
+      <c r="A14" s="67"/>
+      <c r="B14" s="78"/>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -1995,8 +1988,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="68"/>
-      <c r="B15" s="81"/>
+      <c r="A15" s="67"/>
+      <c r="B15" s="80"/>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
@@ -2011,8 +2004,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="68"/>
-      <c r="B16" s="72" t="s">
+      <c r="A16" s="67"/>
+      <c r="B16" s="71" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
@@ -2030,8 +2023,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="68"/>
-      <c r="B17" s="72"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="71"/>
       <c r="C17" t="s">
         <v>12</v>
       </c>
@@ -2046,8 +2039,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="68"/>
-      <c r="B18" s="72"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="71"/>
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -2062,8 +2055,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="68"/>
-      <c r="B19" s="72"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="71"/>
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -2078,8 +2071,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="68"/>
-      <c r="B20" s="72"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="71"/>
       <c r="C20" t="s">
         <v>17</v>
       </c>
@@ -2094,10 +2087,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="67" t="s">
+      <c r="A21" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="71" t="s">
+      <c r="B21" s="70" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2114,8 +2107,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="68"/>
-      <c r="B22" s="72"/>
+      <c r="A22" s="67"/>
+      <c r="B22" s="71"/>
       <c r="C22" t="s">
         <v>13</v>
       </c>
@@ -2130,8 +2123,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="68"/>
-      <c r="B23" s="72"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="71"/>
       <c r="C23" t="s">
         <v>15</v>
       </c>
@@ -2146,8 +2139,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="68"/>
-      <c r="B24" s="72"/>
+      <c r="A24" s="67"/>
+      <c r="B24" s="71"/>
       <c r="C24" t="s">
         <v>22</v>
       </c>
@@ -2162,8 +2155,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="68"/>
-      <c r="B25" s="72"/>
+      <c r="A25" s="67"/>
+      <c r="B25" s="71"/>
       <c r="C25" t="s">
         <v>47</v>
       </c>
@@ -2178,8 +2171,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="68"/>
-      <c r="B26" s="72"/>
+      <c r="A26" s="67"/>
+      <c r="B26" s="71"/>
       <c r="C26" t="s">
         <v>48</v>
       </c>
@@ -2194,8 +2187,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="68"/>
-      <c r="B27" s="72"/>
+      <c r="A27" s="67"/>
+      <c r="B27" s="71"/>
       <c r="C27" t="s">
         <v>17</v>
       </c>
@@ -2210,8 +2203,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="68"/>
-      <c r="B28" s="72"/>
+      <c r="A28" s="67"/>
+      <c r="B28" s="71"/>
       <c r="C28" t="s">
         <v>114</v>
       </c>
@@ -2226,8 +2219,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="68"/>
-      <c r="B29" s="73" t="s">
+      <c r="A29" s="67"/>
+      <c r="B29" s="72" t="s">
         <v>256</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -2244,8 +2237,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="68"/>
-      <c r="B30" s="76"/>
+      <c r="A30" s="67"/>
+      <c r="B30" s="75"/>
       <c r="C30" s="48" t="s">
         <v>23</v>
       </c>
@@ -2261,8 +2254,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="68"/>
-      <c r="B31" s="76"/>
+      <c r="A31" s="67"/>
+      <c r="B31" s="75"/>
       <c r="C31" s="48" t="s">
         <v>18</v>
       </c>
@@ -2277,8 +2270,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="68"/>
-      <c r="B32" s="76"/>
+      <c r="A32" s="67"/>
+      <c r="B32" s="75"/>
       <c r="C32" s="48" t="s">
         <v>19</v>
       </c>
@@ -2293,8 +2286,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="68"/>
-      <c r="B33" s="76"/>
+      <c r="A33" s="67"/>
+      <c r="B33" s="75"/>
       <c r="C33" s="48" t="s">
         <v>47</v>
       </c>
@@ -2309,8 +2302,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="68"/>
-      <c r="B34" s="76"/>
+      <c r="A34" s="67"/>
+      <c r="B34" s="75"/>
       <c r="C34" s="48" t="s">
         <v>48</v>
       </c>
@@ -2325,8 +2318,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="68"/>
-      <c r="B35" s="76"/>
+      <c r="A35" s="67"/>
+      <c r="B35" s="75"/>
       <c r="C35" s="48" t="s">
         <v>115</v>
       </c>
@@ -2341,8 +2334,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="68"/>
-      <c r="B36" s="76"/>
+      <c r="A36" s="67"/>
+      <c r="B36" s="75"/>
       <c r="C36" s="48" t="s">
         <v>114</v>
       </c>
@@ -2357,8 +2350,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="68"/>
-      <c r="B37" s="76"/>
+      <c r="A37" s="67"/>
+      <c r="B37" s="75"/>
       <c r="C37" s="48" t="s">
         <v>15</v>
       </c>
@@ -2373,8 +2366,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="69"/>
-      <c r="B38" s="77"/>
+      <c r="A38" s="68"/>
+      <c r="B38" s="76"/>
       <c r="C38" s="14" t="s">
         <v>17</v>
       </c>
@@ -2389,64 +2382,64 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="67" t="s">
+      <c r="A39" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="55" t="s">
+      <c r="C39" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="55" t="s">
+      <c r="D39" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="56">
+      <c r="E39" s="55">
         <v>0.1699</v>
       </c>
-      <c r="F39" s="55" t="s">
+      <c r="F39" s="54" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="70"/>
-      <c r="B40" s="61" t="s">
+      <c r="A40" s="69"/>
+      <c r="B40" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="C40" s="61" t="s">
+        <v>299</v>
+      </c>
+      <c r="D40" s="61" t="s">
         <v>300</v>
       </c>
-      <c r="C40" s="62" t="s">
-        <v>301</v>
-      </c>
-      <c r="D40" s="62" t="s">
-        <v>302</v>
-      </c>
-      <c r="E40" s="63">
+      <c r="E40" s="62">
         <v>0.2</v>
       </c>
-      <c r="F40" s="62" t="s">
+      <c r="F40" s="61" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="70"/>
-      <c r="B41" s="64" t="s">
+      <c r="A41" s="69"/>
+      <c r="B41" s="63" t="s">
+        <v>295</v>
+      </c>
+      <c r="C41" s="64" t="s">
+        <v>296</v>
+      </c>
+      <c r="D41" s="64" t="s">
         <v>297</v>
       </c>
-      <c r="C41" s="65" t="s">
-        <v>298</v>
-      </c>
-      <c r="D41" s="65" t="s">
-        <v>299</v>
-      </c>
-      <c r="E41" s="66">
+      <c r="E41" s="65">
         <v>5</v>
       </c>
-      <c r="F41" s="65" t="s">
+      <c r="F41" s="64" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="68"/>
-      <c r="B42" s="73" t="s">
+      <c r="A42" s="67"/>
+      <c r="B42" s="72" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2463,8 +2456,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="68"/>
-      <c r="B43" s="72"/>
+      <c r="A43" s="67"/>
+      <c r="B43" s="71"/>
       <c r="C43" t="s">
         <v>12</v>
       </c>
@@ -2479,8 +2472,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="68"/>
-      <c r="B44" s="72"/>
+      <c r="A44" s="67"/>
+      <c r="B44" s="71"/>
       <c r="C44" t="s">
         <v>19</v>
       </c>
@@ -2495,8 +2488,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="68"/>
-      <c r="B45" s="72"/>
+      <c r="A45" s="67"/>
+      <c r="B45" s="71"/>
       <c r="C45" t="s">
         <v>20</v>
       </c>
@@ -2511,8 +2504,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="68"/>
-      <c r="B46" s="72"/>
+      <c r="A46" s="67"/>
+      <c r="B46" s="71"/>
       <c r="C46" t="s">
         <v>15</v>
       </c>
@@ -2527,8 +2520,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="68"/>
-      <c r="B47" s="72"/>
+      <c r="A47" s="67"/>
+      <c r="B47" s="71"/>
       <c r="C47" t="s">
         <v>82</v>
       </c>
@@ -2543,8 +2536,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="68"/>
-      <c r="B48" s="74"/>
+      <c r="A48" s="67"/>
+      <c r="B48" s="73"/>
       <c r="C48" s="5" t="s">
         <v>17</v>
       </c>
@@ -2559,8 +2552,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="68"/>
-      <c r="B49" s="73" t="s">
+      <c r="A49" s="67"/>
+      <c r="B49" s="72" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -2577,8 +2570,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="68"/>
-      <c r="B50" s="72"/>
+      <c r="A50" s="67"/>
+      <c r="B50" s="71"/>
       <c r="C50" t="s">
         <v>12</v>
       </c>
@@ -2593,8 +2586,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="68"/>
-      <c r="B51" s="72"/>
+      <c r="A51" s="67"/>
+      <c r="B51" s="71"/>
       <c r="C51" t="s">
         <v>19</v>
       </c>
@@ -2609,8 +2602,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="68"/>
-      <c r="B52" s="72"/>
+      <c r="A52" s="67"/>
+      <c r="B52" s="71"/>
       <c r="C52" t="s">
         <v>20</v>
       </c>
@@ -2625,8 +2618,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="68"/>
-      <c r="B53" s="72"/>
+      <c r="A53" s="67"/>
+      <c r="B53" s="71"/>
       <c r="C53" t="s">
         <v>15</v>
       </c>
@@ -2641,8 +2634,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="68"/>
-      <c r="B54" s="72"/>
+      <c r="A54" s="67"/>
+      <c r="B54" s="71"/>
       <c r="C54" t="s">
         <v>82</v>
       </c>
@@ -2657,8 +2650,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="69"/>
-      <c r="B55" s="75"/>
+      <c r="A55" s="68"/>
+      <c r="B55" s="74"/>
       <c r="C55" s="14" t="s">
         <v>17</v>
       </c>
@@ -2673,7 +2666,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="67" t="s">
+      <c r="A56" s="66" t="s">
         <v>90</v>
       </c>
       <c r="B56" s="16" t="s">
@@ -2686,14 +2679,14 @@
         <v>92</v>
       </c>
       <c r="E56" s="3">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="68"/>
+      <c r="A57" s="67"/>
       <c r="B57" s="17" t="s">
         <v>93</v>
       </c>
@@ -2711,7 +2704,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="69"/>
+      <c r="A58" s="68"/>
       <c r="B58" s="1" t="s">
         <v>94</v>
       </c>
@@ -2750,7 +2743,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="12" customWidth="1"/>
@@ -2783,10 +2776,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="88" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="92" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="27" t="s">
@@ -2801,8 +2794,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="88"/>
-      <c r="B3" s="83"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="94"/>
       <c r="C3" s="12" t="s">
         <v>135</v>
       </c>
@@ -2815,8 +2808,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="88"/>
-      <c r="B4" s="83"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="94"/>
       <c r="C4" s="12" t="s">
         <v>102</v>
       </c>
@@ -2829,8 +2822,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="88"/>
-      <c r="B5" s="83"/>
+      <c r="A5" s="90"/>
+      <c r="B5" s="94"/>
       <c r="C5" s="12" t="s">
         <v>171</v>
       </c>
@@ -2843,8 +2836,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="83"/>
+      <c r="A6" s="90"/>
+      <c r="B6" s="94"/>
       <c r="C6" s="12" t="s">
         <v>183</v>
       </c>
@@ -2857,8 +2850,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="83"/>
+      <c r="A7" s="90"/>
+      <c r="B7" s="94"/>
       <c r="C7" s="12" t="s">
         <v>201</v>
       </c>
@@ -2871,8 +2864,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="83"/>
+      <c r="A8" s="90"/>
+      <c r="B8" s="94"/>
       <c r="C8" s="12" t="s">
         <v>249</v>
       </c>
@@ -2885,8 +2878,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="83"/>
+      <c r="A9" s="90"/>
+      <c r="B9" s="94"/>
       <c r="C9" s="12" t="s">
         <v>215</v>
       </c>
@@ -2899,8 +2892,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="83"/>
+      <c r="A10" s="90"/>
+      <c r="B10" s="94"/>
       <c r="C10" s="12" t="s">
         <v>239</v>
       </c>
@@ -2913,13 +2906,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="83"/>
+      <c r="A11" s="90"/>
+      <c r="B11" s="94"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="82" t="s">
+      <c r="A12" s="90"/>
+      <c r="B12" s="96" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="36" t="s">
@@ -2934,8 +2927,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="83"/>
+      <c r="A13" s="90"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="12" t="s">
         <v>176</v>
       </c>
@@ -2948,8 +2941,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="83"/>
+      <c r="A14" s="90"/>
+      <c r="B14" s="94"/>
       <c r="C14" s="12" t="s">
         <v>179</v>
       </c>
@@ -2962,8 +2955,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="83"/>
+      <c r="A15" s="90"/>
+      <c r="B15" s="94"/>
       <c r="C15" s="12" t="s">
         <v>180</v>
       </c>
@@ -2976,8 +2969,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="88"/>
-      <c r="B16" s="83"/>
+      <c r="A16" s="90"/>
+      <c r="B16" s="94"/>
       <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
@@ -2990,8 +2983,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="88"/>
-      <c r="B17" s="83"/>
+      <c r="A17" s="90"/>
+      <c r="B17" s="94"/>
       <c r="C17" s="12" t="s">
         <v>183</v>
       </c>
@@ -3004,8 +2997,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="88"/>
-      <c r="B18" s="83"/>
+      <c r="A18" s="90"/>
+      <c r="B18" s="94"/>
       <c r="C18" s="12" t="s">
         <v>201</v>
       </c>
@@ -3018,8 +3011,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="88"/>
-      <c r="B19" s="83"/>
+      <c r="A19" s="90"/>
+      <c r="B19" s="94"/>
       <c r="C19" s="12" t="s">
         <v>249</v>
       </c>
@@ -3032,8 +3025,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="88"/>
-      <c r="B20" s="83"/>
+      <c r="A20" s="90"/>
+      <c r="B20" s="94"/>
       <c r="C20" s="12" t="s">
         <v>215</v>
       </c>
@@ -3046,8 +3039,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
-      <c r="B21" s="83"/>
+      <c r="A21" s="90"/>
+      <c r="B21" s="94"/>
       <c r="C21" s="12" t="s">
         <v>239</v>
       </c>
@@ -3060,16 +3053,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="88"/>
-      <c r="B22" s="85"/>
+      <c r="A22" s="90"/>
+      <c r="B22" s="95"/>
       <c r="C22" s="38"/>
       <c r="D22" s="38"/>
       <c r="E22" s="39"/>
       <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
-      <c r="B23" s="90" t="s">
+      <c r="A23" s="90"/>
+      <c r="B23" s="85" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="12" t="s">
@@ -3084,8 +3077,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="88"/>
-      <c r="B24" s="90"/>
+      <c r="A24" s="90"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="12" t="s">
         <v>135</v>
       </c>
@@ -3098,8 +3091,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="88"/>
-      <c r="B25" s="90"/>
+      <c r="A25" s="90"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="12" t="s">
         <v>102</v>
       </c>
@@ -3112,8 +3105,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="88"/>
-      <c r="B26" s="90"/>
+      <c r="A26" s="90"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="12" t="s">
         <v>173</v>
       </c>
@@ -3126,8 +3119,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="88"/>
-      <c r="B27" s="90"/>
+      <c r="A27" s="90"/>
+      <c r="B27" s="85"/>
       <c r="C27" s="12" t="s">
         <v>183</v>
       </c>
@@ -3140,8 +3133,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="88"/>
-      <c r="B28" s="90"/>
+      <c r="A28" s="90"/>
+      <c r="B28" s="85"/>
       <c r="C28" s="12" t="s">
         <v>201</v>
       </c>
@@ -3154,8 +3147,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="88"/>
-      <c r="B29" s="90"/>
+      <c r="A29" s="90"/>
+      <c r="B29" s="85"/>
       <c r="C29" s="12" t="s">
         <v>249</v>
       </c>
@@ -3168,8 +3161,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="88"/>
-      <c r="B30" s="90"/>
+      <c r="A30" s="90"/>
+      <c r="B30" s="85"/>
       <c r="C30" s="12" t="s">
         <v>215</v>
       </c>
@@ -3182,8 +3175,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="88"/>
-      <c r="B31" s="90"/>
+      <c r="A31" s="90"/>
+      <c r="B31" s="85"/>
       <c r="C31" s="12" t="s">
         <v>239</v>
       </c>
@@ -3196,15 +3189,15 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="88"/>
-      <c r="B32" s="90"/>
+      <c r="A32" s="90"/>
+      <c r="B32" s="85"/>
       <c r="E32" s="34"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="86" t="s">
+      <c r="A33" s="88" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="92" t="s">
+      <c r="B33" s="97" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="27" t="s">
@@ -3215,12 +3208,12 @@
       </c>
       <c r="E33" s="40"/>
       <c r="F33" s="27" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="88"/>
-      <c r="B34" s="90"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="85"/>
       <c r="C34" s="12" t="s">
         <v>139</v>
       </c>
@@ -3229,12 +3222,12 @@
       </c>
       <c r="E34" s="34"/>
       <c r="F34" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="88"/>
-      <c r="B35" s="90"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="85"/>
       <c r="C35" s="12" t="s">
         <v>168</v>
       </c>
@@ -3247,8 +3240,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="88"/>
-      <c r="B36" s="90"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="12" t="s">
         <v>169</v>
       </c>
@@ -3261,8 +3254,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="88"/>
-      <c r="B37" s="90"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="12" t="s">
         <v>183</v>
       </c>
@@ -3275,8 +3268,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="88"/>
-      <c r="B38" s="90"/>
+      <c r="A38" s="90"/>
+      <c r="B38" s="85"/>
       <c r="C38" s="12" t="s">
         <v>201</v>
       </c>
@@ -3289,8 +3282,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="88"/>
-      <c r="B39" s="90"/>
+      <c r="A39" s="90"/>
+      <c r="B39" s="85"/>
       <c r="C39" s="12" t="s">
         <v>249</v>
       </c>
@@ -3303,8 +3296,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="88"/>
-      <c r="B40" s="90"/>
+      <c r="A40" s="90"/>
+      <c r="B40" s="85"/>
       <c r="C40" s="12" t="s">
         <v>215</v>
       </c>
@@ -3317,8 +3310,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="88"/>
-      <c r="B41" s="90"/>
+      <c r="A41" s="90"/>
+      <c r="B41" s="85"/>
       <c r="C41" s="12" t="s">
         <v>239</v>
       </c>
@@ -3331,13 +3324,13 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="88"/>
-      <c r="B42" s="90"/>
+      <c r="A42" s="90"/>
+      <c r="B42" s="85"/>
       <c r="E42" s="34"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="88"/>
-      <c r="B43" s="93" t="s">
+      <c r="A43" s="90"/>
+      <c r="B43" s="84" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="36" t="s">
@@ -3352,8 +3345,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="88"/>
-      <c r="B44" s="90"/>
+      <c r="A44" s="90"/>
+      <c r="B44" s="85"/>
       <c r="C44" s="12" t="s">
         <v>141</v>
       </c>
@@ -3366,8 +3359,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="88"/>
-      <c r="B45" s="83"/>
+      <c r="A45" s="90"/>
+      <c r="B45" s="94"/>
       <c r="C45" s="12" t="s">
         <v>139</v>
       </c>
@@ -3380,8 +3373,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="88"/>
-      <c r="B46" s="83"/>
+      <c r="A46" s="90"/>
+      <c r="B46" s="94"/>
       <c r="C46" s="12" t="s">
         <v>135</v>
       </c>
@@ -3394,8 +3387,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="88"/>
-      <c r="B47" s="83"/>
+      <c r="A47" s="90"/>
+      <c r="B47" s="94"/>
       <c r="C47" s="12" t="s">
         <v>156</v>
       </c>
@@ -3408,8 +3401,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="88"/>
-      <c r="B48" s="83"/>
+      <c r="A48" s="90"/>
+      <c r="B48" s="94"/>
       <c r="C48" s="12" t="s">
         <v>157</v>
       </c>
@@ -3422,8 +3415,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="88"/>
-      <c r="B49" s="83"/>
+      <c r="A49" s="90"/>
+      <c r="B49" s="94"/>
       <c r="C49" s="12" t="s">
         <v>183</v>
       </c>
@@ -3436,8 +3429,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="88"/>
-      <c r="B50" s="83"/>
+      <c r="A50" s="90"/>
+      <c r="B50" s="94"/>
       <c r="C50" s="12" t="s">
         <v>201</v>
       </c>
@@ -3450,8 +3443,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="88"/>
-      <c r="B51" s="83"/>
+      <c r="A51" s="90"/>
+      <c r="B51" s="94"/>
       <c r="C51" s="12" t="s">
         <v>249</v>
       </c>
@@ -3464,8 +3457,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="88"/>
-      <c r="B52" s="83"/>
+      <c r="A52" s="90"/>
+      <c r="B52" s="94"/>
       <c r="C52" s="12" t="s">
         <v>215</v>
       </c>
@@ -3478,8 +3471,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="88"/>
-      <c r="B53" s="83"/>
+      <c r="A53" s="90"/>
+      <c r="B53" s="94"/>
       <c r="C53" s="12" t="s">
         <v>239</v>
       </c>
@@ -3493,17 +3486,17 @@
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="91"/>
-      <c r="B54" s="94"/>
+      <c r="B54" s="98"/>
       <c r="C54" s="42"/>
       <c r="D54" s="42"/>
       <c r="E54" s="43"/>
       <c r="F54" s="42"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="86" t="s">
+      <c r="A55" s="88" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="89" t="s">
+      <c r="B55" s="92" t="s">
         <v>87</v>
       </c>
       <c r="C55" s="27" t="s">
@@ -3518,8 +3511,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="88"/>
-      <c r="B56" s="83"/>
+      <c r="A56" s="90"/>
+      <c r="B56" s="94"/>
       <c r="C56" s="12" t="s">
         <v>199</v>
       </c>
@@ -3532,51 +3525,51 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="88"/>
-      <c r="B57" s="85"/>
+      <c r="A57" s="90"/>
+      <c r="B57" s="95"/>
       <c r="E57" s="32"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="88"/>
-      <c r="B58" s="95" t="s">
+      <c r="A58" s="90"/>
+      <c r="B58" s="81" t="s">
+        <v>301</v>
+      </c>
+      <c r="C58" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="D58" s="56" t="s">
         <v>303</v>
       </c>
-      <c r="C58" s="57" t="s">
+      <c r="E58" s="57"/>
+      <c r="F58" s="56" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="90"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="D59" s="58" t="s">
         <v>304</v>
       </c>
-      <c r="D58" s="57" t="s">
-        <v>305</v>
-      </c>
-      <c r="E58" s="58"/>
-      <c r="F58" s="57" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="88"/>
-      <c r="B59" s="96"/>
-      <c r="C59" s="59" t="s">
-        <v>199</v>
-      </c>
-      <c r="D59" s="59" t="s">
-        <v>306</v>
-      </c>
-      <c r="E59" s="60"/>
-      <c r="F59" s="59" t="s">
+      <c r="E59" s="59"/>
+      <c r="F59" s="58" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="88"/>
-      <c r="B60" s="97"/>
-      <c r="C60" s="59"/>
-      <c r="D60" s="59"/>
-      <c r="E60" s="60"/>
-      <c r="F60" s="59"/>
+      <c r="A60" s="90"/>
+      <c r="B60" s="83"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="59"/>
+      <c r="F60" s="58"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="88"/>
-      <c r="B61" s="93" t="s">
+      <c r="A61" s="90"/>
+      <c r="B61" s="84" t="s">
         <v>6</v>
       </c>
       <c r="C61" s="36" t="s">
@@ -3591,8 +3584,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="88"/>
-      <c r="B62" s="90"/>
+      <c r="A62" s="90"/>
+      <c r="B62" s="85"/>
       <c r="C62" s="12" t="s">
         <v>135</v>
       </c>
@@ -3605,8 +3598,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="88"/>
-      <c r="B63" s="90"/>
+      <c r="A63" s="90"/>
+      <c r="B63" s="85"/>
       <c r="C63" s="12" t="s">
         <v>151</v>
       </c>
@@ -3619,8 +3612,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="88"/>
-      <c r="B64" s="90"/>
+      <c r="A64" s="90"/>
+      <c r="B64" s="85"/>
       <c r="C64" s="12" t="s">
         <v>183</v>
       </c>
@@ -3633,8 +3626,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="88"/>
-      <c r="B65" s="90"/>
+      <c r="A65" s="90"/>
+      <c r="B65" s="85"/>
       <c r="C65" s="12" t="s">
         <v>201</v>
       </c>
@@ -3647,8 +3640,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="88"/>
-      <c r="B66" s="90"/>
+      <c r="A66" s="90"/>
+      <c r="B66" s="85"/>
       <c r="C66" s="12" t="s">
         <v>209</v>
       </c>
@@ -3661,8 +3654,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="88"/>
-      <c r="B67" s="90"/>
+      <c r="A67" s="90"/>
+      <c r="B67" s="85"/>
       <c r="C67" s="12" t="s">
         <v>249</v>
       </c>
@@ -3675,8 +3668,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="88"/>
-      <c r="B68" s="90"/>
+      <c r="A68" s="90"/>
+      <c r="B68" s="85"/>
       <c r="C68" s="12" t="s">
         <v>215</v>
       </c>
@@ -3689,8 +3682,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="88"/>
-      <c r="B69" s="90"/>
+      <c r="A69" s="90"/>
+      <c r="B69" s="85"/>
       <c r="C69" s="12" t="s">
         <v>239</v>
       </c>
@@ -3703,12 +3696,12 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="88"/>
-      <c r="B70" s="98"/>
+      <c r="A70" s="90"/>
+      <c r="B70" s="86"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="88"/>
-      <c r="B71" s="93" t="s">
+      <c r="A71" s="90"/>
+      <c r="B71" s="84" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="36" t="s">
@@ -3723,8 +3716,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="88"/>
-      <c r="B72" s="90"/>
+      <c r="A72" s="90"/>
+      <c r="B72" s="85"/>
       <c r="C72" s="12" t="s">
         <v>136</v>
       </c>
@@ -3737,8 +3730,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="88"/>
-      <c r="B73" s="90"/>
+      <c r="A73" s="90"/>
+      <c r="B73" s="85"/>
       <c r="C73" s="12" t="s">
         <v>149</v>
       </c>
@@ -3751,8 +3744,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="88"/>
-      <c r="B74" s="90"/>
+      <c r="A74" s="90"/>
+      <c r="B74" s="85"/>
       <c r="C74" s="12" t="s">
         <v>183</v>
       </c>
@@ -3765,8 +3758,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="88"/>
-      <c r="B75" s="90"/>
+      <c r="A75" s="90"/>
+      <c r="B75" s="85"/>
       <c r="C75" s="12" t="s">
         <v>201</v>
       </c>
@@ -3779,8 +3772,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="88"/>
-      <c r="B76" s="90"/>
+      <c r="A76" s="90"/>
+      <c r="B76" s="85"/>
       <c r="C76" s="12" t="s">
         <v>209</v>
       </c>
@@ -3793,8 +3786,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="88"/>
-      <c r="B77" s="90"/>
+      <c r="A77" s="90"/>
+      <c r="B77" s="85"/>
       <c r="C77" s="12" t="s">
         <v>249</v>
       </c>
@@ -3807,8 +3800,8 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="88"/>
-      <c r="B78" s="90"/>
+      <c r="A78" s="90"/>
+      <c r="B78" s="85"/>
       <c r="C78" s="12" t="s">
         <v>215</v>
       </c>
@@ -3821,8 +3814,8 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="88"/>
-      <c r="B79" s="90"/>
+      <c r="A79" s="90"/>
+      <c r="B79" s="85"/>
       <c r="C79" s="12" t="s">
         <v>239</v>
       </c>
@@ -3836,13 +3829,13 @@
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="91"/>
-      <c r="B80" s="99"/>
+      <c r="B80" s="87"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="86" t="s">
+      <c r="A81" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="89" t="s">
+      <c r="B81" s="92" t="s">
         <v>87</v>
       </c>
       <c r="C81" s="27" t="s">
@@ -3857,313 +3850,313 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="87"/>
-      <c r="B82" s="84"/>
-      <c r="C82" s="52" t="s">
-        <v>291</v>
-      </c>
-      <c r="D82" s="52" t="s">
-        <v>290</v>
-      </c>
-      <c r="E82" s="53"/>
-      <c r="F82" s="52" t="s">
+      <c r="A82" s="90"/>
+      <c r="B82" s="94"/>
+      <c r="C82" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E82" s="34"/>
+      <c r="F82" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="88"/>
-      <c r="B83" s="83"/>
-      <c r="C83" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>191</v>
-      </c>
+      <c r="A83" s="90"/>
+      <c r="B83" s="95"/>
       <c r="E83" s="34"/>
-      <c r="F83" s="12" t="s">
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="90"/>
+      <c r="B84" s="96" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="D84" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="E84" s="41"/>
+      <c r="F84" s="36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="90"/>
+      <c r="B85" s="94"/>
+      <c r="C85" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E85" s="34"/>
+      <c r="F85" s="12" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="88"/>
-      <c r="B84" s="85"/>
-      <c r="E84" s="34"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="88"/>
-      <c r="B85" s="82" t="s">
-        <v>93</v>
-      </c>
-      <c r="C85" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="D85" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="E85" s="41"/>
-      <c r="F85" s="36" t="s">
-        <v>163</v>
-      </c>
-    </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="88"/>
-      <c r="B86" s="83"/>
-      <c r="C86" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E86" s="34"/>
-      <c r="F86" s="12" t="s">
-        <v>194</v>
-      </c>
+      <c r="A86" s="90"/>
+      <c r="B86" s="95"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="38"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="88"/>
-      <c r="B87" s="85"/>
-      <c r="C87" s="38"/>
-      <c r="D87" s="38"/>
-      <c r="E87" s="39"/>
-      <c r="F87" s="38"/>
+      <c r="A87" s="90"/>
+      <c r="B87" s="96" t="s">
+        <v>94</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E87" s="34"/>
+      <c r="F87" s="12" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="88"/>
-      <c r="B88" s="82" t="s">
-        <v>94</v>
-      </c>
+      <c r="A88" s="90"/>
+      <c r="B88" s="94"/>
       <c r="C88" s="12" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="E88" s="34"/>
       <c r="F88" s="12" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="88"/>
-      <c r="B89" s="83"/>
-      <c r="C89" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="E89" s="34"/>
-      <c r="F89" s="12" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="91"/>
-      <c r="B90" s="94"/>
-      <c r="C90" s="42"/>
-      <c r="D90" s="42"/>
-      <c r="E90" s="43"/>
-      <c r="F90" s="42"/>
+    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="91"/>
+      <c r="B89" s="98"/>
+      <c r="C89" s="42"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="43"/>
+      <c r="F89" s="42"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="88" t="s">
+        <v>211</v>
+      </c>
+      <c r="B90" s="92" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="D90" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="E90" s="27"/>
+      <c r="F90" s="27" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="86" t="s">
-        <v>211</v>
-      </c>
-      <c r="B91" s="89" t="s">
-        <v>15</v>
-      </c>
-      <c r="C91" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="D91" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="E91" s="27"/>
-      <c r="F91" s="27" t="s">
+      <c r="A91" s="89"/>
+      <c r="B91" s="94"/>
+      <c r="C91" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F91" s="12" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="87"/>
-      <c r="B92" s="83"/>
-      <c r="C92" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F92" s="12" t="s">
-        <v>182</v>
-      </c>
+      <c r="A92" s="89"/>
+      <c r="B92" s="95"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="38"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="87"/>
-      <c r="B93" s="85"/>
-      <c r="C93" s="38"/>
-      <c r="D93" s="38"/>
-      <c r="E93" s="38"/>
-      <c r="F93" s="38"/>
+      <c r="A93" s="89"/>
+      <c r="B93" s="96" t="s">
+        <v>234</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="87"/>
-      <c r="B94" s="82" t="s">
-        <v>234</v>
-      </c>
+      <c r="A94" s="89"/>
+      <c r="B94" s="94"/>
       <c r="C94" s="12" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="F94" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="87"/>
-      <c r="B95" s="83"/>
+      <c r="A95" s="89"/>
+      <c r="B95" s="94"/>
       <c r="C95" s="12" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F95" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="87"/>
-      <c r="B96" s="83"/>
+      <c r="A96" s="89"/>
+      <c r="B96" s="94"/>
       <c r="C96" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F96" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="87"/>
-      <c r="B97" s="83"/>
+      <c r="A97" s="89"/>
+      <c r="B97" s="94"/>
       <c r="C97" s="12" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F97" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="87"/>
-      <c r="B98" s="83"/>
+      <c r="A98" s="89"/>
+      <c r="B98" s="94"/>
       <c r="C98" s="12" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F98" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="87"/>
-      <c r="B99" s="83"/>
-      <c r="C99" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="F99" s="12" t="s">
-        <v>194</v>
+      <c r="A99" s="89"/>
+      <c r="B99" s="96" t="s">
+        <v>263</v>
+      </c>
+      <c r="C99" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="D99" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="E99" s="36"/>
+      <c r="F99" s="36" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="87"/>
-      <c r="B100" s="82" t="s">
-        <v>263</v>
-      </c>
-      <c r="C100" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="D100" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="E100" s="36"/>
-      <c r="F100" s="36" t="s">
+      <c r="A100" s="89"/>
+      <c r="B100" s="93"/>
+      <c r="C100" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="D100" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="E100" s="52"/>
+      <c r="F100" s="52" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="87"/>
-      <c r="B101" s="84"/>
+      <c r="A101" s="89"/>
+      <c r="B101" s="93"/>
       <c r="C101" s="52" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D101" s="52" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E101" s="52"/>
       <c r="F101" s="52" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="87"/>
-      <c r="B102" s="84"/>
+      <c r="A102" s="89"/>
+      <c r="B102" s="93"/>
       <c r="C102" s="52" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="D102" s="52" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E102" s="52"/>
       <c r="F102" s="52" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="87"/>
-      <c r="B103" s="84"/>
+      <c r="A103" s="89"/>
+      <c r="B103" s="93"/>
       <c r="C103" s="52" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D103" s="52" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="E103" s="52"/>
       <c r="F103" s="52" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="87"/>
-      <c r="B104" s="84"/>
+      <c r="A104" s="89"/>
+      <c r="B104" s="93"/>
       <c r="C104" s="52" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D104" s="52" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E104" s="52"/>
       <c r="F104" s="52" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="87"/>
-      <c r="B105" s="84"/>
+      <c r="A105" s="89"/>
+      <c r="B105" s="93"/>
       <c r="C105" s="52" t="s">
-        <v>280</v>
-      </c>
-      <c r="D105" s="52" t="s">
-        <v>268</v>
+        <v>257</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>279</v>
       </c>
       <c r="E105" s="52"/>
       <c r="F105" s="52" t="s">
@@ -4171,71 +4164,71 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="87"/>
-      <c r="B106" s="84"/>
+      <c r="A106" s="89"/>
+      <c r="B106" s="93"/>
       <c r="C106" s="52" t="s">
-        <v>257</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>279</v>
+        <v>261</v>
+      </c>
+      <c r="D106" s="52" t="s">
+        <v>270</v>
       </c>
       <c r="E106" s="52"/>
-      <c r="F106" s="52" t="s">
+      <c r="F106" s="12" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="87"/>
-      <c r="B107" s="84"/>
+      <c r="A107" s="89"/>
+      <c r="B107" s="93"/>
       <c r="C107" s="52" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D107" s="52" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E107" s="52"/>
-      <c r="F107" s="12" t="s">
+      <c r="F107" s="52" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="89"/>
+      <c r="B108" s="96" t="s">
+        <v>281</v>
+      </c>
+      <c r="C108" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="D108" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="E108" s="36"/>
+      <c r="F108" s="36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="89"/>
+      <c r="B109" s="93"/>
+      <c r="C109" s="52" t="s">
+        <v>284</v>
+      </c>
+      <c r="D109" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="E109" s="52"/>
+      <c r="F109" s="52" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="87"/>
-      <c r="B108" s="84"/>
-      <c r="C108" s="52" t="s">
-        <v>262</v>
-      </c>
-      <c r="D108" s="52" t="s">
-        <v>271</v>
-      </c>
-      <c r="E108" s="52"/>
-      <c r="F108" s="52" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="87"/>
-      <c r="B109" s="82" t="s">
-        <v>281</v>
-      </c>
-      <c r="C109" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="D109" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="E109" s="36"/>
-      <c r="F109" s="36" t="s">
-        <v>265</v>
-      </c>
-    </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="87"/>
-      <c r="B110" s="84"/>
+      <c r="A110" s="89"/>
+      <c r="B110" s="93"/>
       <c r="C110" s="52" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D110" s="52" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E110" s="52"/>
       <c r="F110" s="52" t="s">
@@ -4243,79 +4236,59 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="87"/>
-      <c r="B111" s="84"/>
-      <c r="C111" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="D111" s="52" t="s">
-        <v>288</v>
-      </c>
-      <c r="E111" s="52"/>
-      <c r="F111" s="52" t="s">
-        <v>269</v>
+      <c r="A111" s="89"/>
+      <c r="B111" s="93"/>
+      <c r="C111" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="87"/>
-      <c r="B112" s="84"/>
-      <c r="C112" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="F112" s="12" t="s">
-        <v>272</v>
-      </c>
+      <c r="A112" s="89"/>
+      <c r="B112" s="95"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="87"/>
-      <c r="B113" s="85"/>
+      <c r="A113" s="89"/>
+      <c r="B113" s="96" t="s">
+        <v>290</v>
+      </c>
+      <c r="C113" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="D113" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="E113" s="36"/>
+      <c r="F113" s="36" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="87"/>
-      <c r="B114" s="82" t="s">
-        <v>292</v>
-      </c>
-      <c r="C114" s="36" t="s">
+      <c r="A114" s="89"/>
+      <c r="B114" s="94"/>
+      <c r="C114" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="D114" s="36" t="s">
+      <c r="D114" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="E114" s="36"/>
-      <c r="F114" s="36" t="s">
+      <c r="F114" s="12" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="87"/>
-      <c r="B115" s="83"/>
-      <c r="C115" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="87"/>
+      <c r="A115" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B70"/>
-    <mergeCell ref="B71:B80"/>
-    <mergeCell ref="A81:A90"/>
-    <mergeCell ref="B81:B84"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="B109:B113"/>
-    <mergeCell ref="A91:A116"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="B108:B112"/>
+    <mergeCell ref="A90:A115"/>
     <mergeCell ref="A2:A32"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -4323,12 +4296,18 @@
     <mergeCell ref="A33:A54"/>
     <mergeCell ref="B33:B42"/>
     <mergeCell ref="B43:B54"/>
-    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="B87:B89"/>
     <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B94:B99"/>
-    <mergeCell ref="B100:B108"/>
-    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="B99:B107"/>
+    <mergeCell ref="B90:B92"/>
     <mergeCell ref="A55:A80"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B70"/>
+    <mergeCell ref="B71:B80"/>
+    <mergeCell ref="A81:A89"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
